--- a/research/traditional_assets/database/data/philippines/philippines_packaging_container.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_packaging_container.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08819996634617783</v>
+        <v>0.08801321643031237</v>
       </c>
       <c r="C2">
-        <v>86.58617949637028</v>
+        <v>86.10727083568197</v>
       </c>
       <c r="D2">
-        <v>84.78617949637028</v>
+        <v>85.16127083568198</v>
       </c>
       <c r="E2">
-        <v>-47</v>
+        <v>-46.146</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8540000000000001</v>
       </c>
       <c r="G2">
         <v>1.8</v>
@@ -1439,28 +1439,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0429562</v>
       </c>
       <c r="N2">
-        <v>6.436666666666667</v>
+        <v>6.393710466666667</v>
       </c>
       <c r="O2">
-        <v>1.609166666666667</v>
+        <v>1.598427616666667</v>
       </c>
       <c r="P2">
-        <v>4.8275</v>
+        <v>4.79528285</v>
       </c>
       <c r="Q2">
-        <v>7.4575</v>
+        <v>7.425282849999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08819996634617783</v>
+        <v>0.08852117821243674</v>
       </c>
       <c r="T2">
-        <v>0.6169711731246059</v>
+        <v>0.6216451971634287</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>149.8425528018462</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08801321643031237</v>
+        <v>0.08782646651444694</v>
       </c>
       <c r="C3">
-        <v>86.10727083568197</v>
+        <v>85.63169570654496</v>
       </c>
       <c r="D3">
-        <v>85.16127083568198</v>
+        <v>85.53969570654496</v>
       </c>
       <c r="E3">
-        <v>-46.146</v>
+        <v>-45.292</v>
       </c>
       <c r="F3">
-        <v>0.8540000000000001</v>
+        <v>1.708</v>
       </c>
       <c r="G3">
         <v>1.8</v>
@@ -1521,28 +1521,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M3">
-        <v>0.0429562</v>
+        <v>0.0859124</v>
       </c>
       <c r="N3">
-        <v>6.393710466666667</v>
+        <v>6.350754266666667</v>
       </c>
       <c r="O3">
-        <v>1.598427616666667</v>
+        <v>1.587688566666667</v>
       </c>
       <c r="P3">
-        <v>4.79528285</v>
+        <v>4.7630657</v>
       </c>
       <c r="Q3">
-        <v>7.425282849999999</v>
+        <v>7.3930657</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08852117821243674</v>
+        <v>0.08884894542290503</v>
       </c>
       <c r="T3">
-        <v>0.6216451971634287</v>
+        <v>0.6264146094479418</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>149.8425528018462</v>
+        <v>74.92127640092311</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08782646651444694</v>
+        <v>0.08763971659858148</v>
       </c>
       <c r="C4">
-        <v>85.63169570654496</v>
+        <v>85.15949874621698</v>
       </c>
       <c r="D4">
-        <v>85.53969570654496</v>
+        <v>85.92149874621698</v>
       </c>
       <c r="E4">
-        <v>-45.292</v>
+        <v>-44.438</v>
       </c>
       <c r="F4">
-        <v>1.708</v>
+        <v>2.562</v>
       </c>
       <c r="G4">
         <v>1.8</v>
@@ -1603,28 +1603,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M4">
-        <v>0.0859124</v>
+        <v>0.1288686</v>
       </c>
       <c r="N4">
-        <v>6.350754266666667</v>
+        <v>6.307798066666667</v>
       </c>
       <c r="O4">
-        <v>1.587688566666667</v>
+        <v>1.576949516666667</v>
       </c>
       <c r="P4">
-        <v>4.7630657</v>
+        <v>4.73084855</v>
       </c>
       <c r="Q4">
-        <v>7.3930657</v>
+        <v>7.36084855</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08884894542290503</v>
+        <v>0.08918347072018709</v>
       </c>
       <c r="T4">
-        <v>0.6264146094479418</v>
+        <v>0.6312823601300735</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>74.92127640092311</v>
+        <v>49.94751760061541</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08763971659858148</v>
+        <v>0.08745296668271604</v>
       </c>
       <c r="C5">
-        <v>85.15949874621698</v>
+        <v>84.6907253924752</v>
       </c>
       <c r="D5">
-        <v>85.92149874621698</v>
+        <v>86.3067253924752</v>
       </c>
       <c r="E5">
-        <v>-44.438</v>
+        <v>-43.584</v>
       </c>
       <c r="F5">
-        <v>2.562</v>
+        <v>3.416</v>
       </c>
       <c r="G5">
         <v>1.8</v>
@@ -1685,28 +1685,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M5">
-        <v>0.1288686</v>
+        <v>0.1718248</v>
       </c>
       <c r="N5">
-        <v>6.307798066666667</v>
+        <v>6.264841866666666</v>
       </c>
       <c r="O5">
-        <v>1.576949516666667</v>
+        <v>1.566210466666667</v>
       </c>
       <c r="P5">
-        <v>4.73084855</v>
+        <v>4.6986314</v>
       </c>
       <c r="Q5">
-        <v>7.36084855</v>
+        <v>7.3286314</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08918347072018709</v>
+        <v>0.08952496529449588</v>
       </c>
       <c r="T5">
-        <v>0.6312823601300735</v>
+        <v>0.6362515222847499</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>49.94751760061541</v>
+        <v>37.46063820046155</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08745296668271604</v>
+        <v>0.08726621676685059</v>
       </c>
       <c r="C6">
-        <v>84.6907253924752</v>
+        <v>84.22542190164295</v>
       </c>
       <c r="D6">
-        <v>86.3067253924752</v>
+        <v>86.69542190164294</v>
       </c>
       <c r="E6">
-        <v>-43.584</v>
+        <v>-42.73</v>
       </c>
       <c r="F6">
-        <v>3.416</v>
+        <v>4.27</v>
       </c>
       <c r="G6">
         <v>1.8</v>
@@ -1767,28 +1767,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M6">
-        <v>0.1718248</v>
+        <v>0.214781</v>
       </c>
       <c r="N6">
-        <v>6.264841866666666</v>
+        <v>6.221885666666666</v>
       </c>
       <c r="O6">
-        <v>1.566210466666667</v>
+        <v>1.555471416666667</v>
       </c>
       <c r="P6">
-        <v>4.6986314</v>
+        <v>4.66641425</v>
       </c>
       <c r="Q6">
-        <v>7.3286314</v>
+        <v>7.29641425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08952496529449588</v>
+        <v>0.08987364922826378</v>
       </c>
       <c r="T6">
-        <v>0.6362515222847499</v>
+        <v>0.6413252983795246</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>37.46063820046155</v>
+        <v>29.96851056036924</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08726621676685059</v>
+        <v>0.08707946685098514</v>
       </c>
       <c r="C7">
-        <v>84.22542190164295</v>
+        <v>83.76363536710501</v>
       </c>
       <c r="D7">
-        <v>86.69542190164294</v>
+        <v>87.08763536710501</v>
       </c>
       <c r="E7">
-        <v>-42.73</v>
+        <v>-41.876</v>
       </c>
       <c r="F7">
-        <v>4.27</v>
+        <v>5.124000000000001</v>
       </c>
       <c r="G7">
         <v>1.8</v>
@@ -1849,28 +1849,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M7">
-        <v>0.214781</v>
+        <v>0.2577372</v>
       </c>
       <c r="N7">
-        <v>6.221885666666666</v>
+        <v>6.178929466666666</v>
       </c>
       <c r="O7">
-        <v>1.555471416666667</v>
+        <v>1.544732366666667</v>
       </c>
       <c r="P7">
-        <v>4.66641425</v>
+        <v>4.6341971</v>
       </c>
       <c r="Q7">
-        <v>7.29641425</v>
+        <v>7.2641971</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08987364922826378</v>
+        <v>0.09022975196913313</v>
       </c>
       <c r="T7">
-        <v>0.6413252983795246</v>
+        <v>0.6465070271571668</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.96851056036924</v>
+        <v>24.9737588003077</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08707946685098514</v>
+        <v>0.08689271693511971</v>
       </c>
       <c r="C8">
-        <v>83.76363536710501</v>
+        <v>83.30541373832841</v>
       </c>
       <c r="D8">
-        <v>87.08763536710501</v>
+        <v>87.48341373832841</v>
       </c>
       <c r="E8">
-        <v>-41.876</v>
+        <v>-41.022</v>
       </c>
       <c r="F8">
-        <v>5.124000000000001</v>
+        <v>5.978</v>
       </c>
       <c r="G8">
         <v>1.8</v>
@@ -1931,28 +1931,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M8">
-        <v>0.2577372</v>
+        <v>0.3006934</v>
       </c>
       <c r="N8">
-        <v>6.178929466666666</v>
+        <v>6.135973266666666</v>
       </c>
       <c r="O8">
-        <v>1.544732366666667</v>
+        <v>1.533993316666667</v>
       </c>
       <c r="P8">
-        <v>4.6341971</v>
+        <v>4.60197995</v>
       </c>
       <c r="Q8">
-        <v>7.2641971</v>
+        <v>7.231979949999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09022975196913313</v>
+        <v>0.09059351283346205</v>
       </c>
       <c r="T8">
-        <v>0.6465070271571668</v>
+        <v>0.6518001909622853</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.9737588003077</v>
+        <v>21.40607897169232</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0868927169351197</v>
+        <v>0.08670596701925426</v>
       </c>
       <c r="C9">
-        <v>83.30541373832844</v>
+        <v>82.85080584040401</v>
       </c>
       <c r="D9">
-        <v>87.48341373832844</v>
+        <v>87.88280584040402</v>
       </c>
       <c r="E9">
-        <v>-41.022</v>
+        <v>-40.168</v>
       </c>
       <c r="F9">
-        <v>5.978000000000001</v>
+        <v>6.832000000000001</v>
       </c>
       <c r="G9">
         <v>1.8</v>
@@ -2013,28 +2013,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M9">
-        <v>0.3006934</v>
+        <v>0.3436496</v>
       </c>
       <c r="N9">
-        <v>6.135973266666666</v>
+        <v>6.093017066666667</v>
       </c>
       <c r="O9">
-        <v>1.533993316666667</v>
+        <v>1.523254266666667</v>
       </c>
       <c r="P9">
-        <v>4.60197995</v>
+        <v>4.569762799999999</v>
       </c>
       <c r="Q9">
-        <v>7.231979949999999</v>
+        <v>7.199762799999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09059351283346205</v>
+        <v>0.09096518154266768</v>
       </c>
       <c r="T9">
-        <v>0.6518001909622853</v>
+        <v>0.6572084235457759</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>21.40607897169232</v>
+        <v>18.73031910023078</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08670596701925426</v>
+        <v>0.08651921710338882</v>
       </c>
       <c r="C10">
-        <v>82.85080584040401</v>
+        <v>82.39986139412557</v>
       </c>
       <c r="D10">
-        <v>87.88280584040402</v>
+        <v>88.28586139412556</v>
       </c>
       <c r="E10">
-        <v>-40.168</v>
+        <v>-39.314</v>
       </c>
       <c r="F10">
-        <v>6.832000000000001</v>
+        <v>7.686</v>
       </c>
       <c r="G10">
         <v>1.8</v>
@@ -2095,28 +2095,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M10">
-        <v>0.3436496</v>
+        <v>0.3866058</v>
       </c>
       <c r="N10">
-        <v>6.093017066666667</v>
+        <v>6.050060866666667</v>
       </c>
       <c r="O10">
-        <v>1.523254266666667</v>
+        <v>1.512515216666667</v>
       </c>
       <c r="P10">
-        <v>4.569762799999999</v>
+        <v>4.53754565</v>
       </c>
       <c r="Q10">
-        <v>7.199762799999999</v>
+        <v>7.16754565</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09096518154266768</v>
+        <v>0.09134501879493276</v>
       </c>
       <c r="T10">
-        <v>0.6572084235457759</v>
+        <v>0.6627355183838486</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.73031910023078</v>
+        <v>16.64917253353847</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08651921710338882</v>
+        <v>0.08633246718752337</v>
       </c>
       <c r="C11">
-        <v>82.39986139412557</v>
+        <v>81.95263103662433</v>
       </c>
       <c r="D11">
-        <v>88.28586139412556</v>
+        <v>88.69263103662432</v>
       </c>
       <c r="E11">
-        <v>-39.314</v>
+        <v>-38.46</v>
       </c>
       <c r="F11">
-        <v>7.686</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G11">
         <v>1.8</v>
@@ -2177,28 +2177,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M11">
-        <v>0.3866058</v>
+        <v>0.4295619999999999</v>
       </c>
       <c r="N11">
-        <v>6.050060866666667</v>
+        <v>6.007104666666667</v>
       </c>
       <c r="O11">
-        <v>1.512515216666667</v>
+        <v>1.501776166666667</v>
       </c>
       <c r="P11">
-        <v>4.53754565</v>
+        <v>4.5053285</v>
       </c>
       <c r="Q11">
-        <v>7.16754565</v>
+        <v>7.1353285</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09134501879493276</v>
+        <v>0.09173329687502596</v>
       </c>
       <c r="T11">
-        <v>0.6627355183838486</v>
+        <v>0.6683854375516564</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.64917253353847</v>
+        <v>14.98425528018462</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08633246718752337</v>
+        <v>0.08614571727165793</v>
       </c>
       <c r="C12">
-        <v>81.95263103662431</v>
+        <v>81.50916634257635</v>
       </c>
       <c r="D12">
-        <v>88.69263103662432</v>
+        <v>89.10316634257636</v>
       </c>
       <c r="E12">
-        <v>-38.46</v>
+        <v>-37.606</v>
       </c>
       <c r="F12">
-        <v>8.540000000000001</v>
+        <v>9.394</v>
       </c>
       <c r="G12">
         <v>1.8</v>
@@ -2259,28 +2259,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M12">
-        <v>0.429562</v>
+        <v>0.4725182</v>
       </c>
       <c r="N12">
-        <v>6.007104666666667</v>
+        <v>5.964148466666667</v>
       </c>
       <c r="O12">
-        <v>1.501776166666667</v>
+        <v>1.491037116666667</v>
       </c>
       <c r="P12">
-        <v>4.5053285</v>
+        <v>4.47311135</v>
       </c>
       <c r="Q12">
-        <v>7.1353285</v>
+        <v>7.10311135</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09173329687502596</v>
+        <v>0.09213030030523363</v>
       </c>
       <c r="T12">
-        <v>0.6683854375516564</v>
+        <v>0.6741623211951453</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.98425528018462</v>
+        <v>13.62205025471329</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08614571727165793</v>
+        <v>0.08609396735579249</v>
       </c>
       <c r="C13">
-        <v>81.50916634257635</v>
+        <v>80.76960236524091</v>
       </c>
       <c r="D13">
-        <v>89.10316634257636</v>
+        <v>89.21760236524092</v>
       </c>
       <c r="E13">
-        <v>-37.606</v>
+        <v>-36.752</v>
       </c>
       <c r="F13">
-        <v>9.394</v>
+        <v>10.248</v>
       </c>
       <c r="G13">
         <v>1.8</v>
@@ -2341,45 +2341,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M13">
-        <v>0.4725182</v>
+        <v>0.5308464000000001</v>
       </c>
       <c r="N13">
-        <v>5.964148466666667</v>
+        <v>5.905820266666667</v>
       </c>
       <c r="O13">
-        <v>1.491037116666667</v>
+        <v>1.476455066666667</v>
       </c>
       <c r="P13">
-        <v>4.47311135</v>
+        <v>4.4293652</v>
       </c>
       <c r="Q13">
-        <v>7.10311135</v>
+        <v>7.0593652</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09213030030523363</v>
+        <v>0.09253632654067327</v>
       </c>
       <c r="T13">
-        <v>0.6741623211951453</v>
+        <v>0.6800704976487133</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.62205025471329</v>
+        <v>12.12529022833472</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08609396735579249</v>
+        <v>0.08591846743992704</v>
       </c>
       <c r="C14">
-        <v>80.76960236524091</v>
+        <v>80.30588850297194</v>
       </c>
       <c r="D14">
-        <v>89.21760236524092</v>
+        <v>89.60788850297195</v>
       </c>
       <c r="E14">
-        <v>-36.752</v>
+        <v>-35.898</v>
       </c>
       <c r="F14">
-        <v>10.248</v>
+        <v>11.102</v>
       </c>
       <c r="G14">
         <v>1.8</v>
@@ -2423,28 +2423,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M14">
-        <v>0.5308464000000001</v>
+        <v>0.5750836</v>
       </c>
       <c r="N14">
-        <v>5.905820266666667</v>
+        <v>5.861583066666666</v>
       </c>
       <c r="O14">
-        <v>1.476455066666667</v>
+        <v>1.465395766666667</v>
       </c>
       <c r="P14">
-        <v>4.4293652</v>
+        <v>4.396187299999999</v>
       </c>
       <c r="Q14">
-        <v>7.0593652</v>
+        <v>7.026187299999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09253632654067327</v>
+        <v>0.09295168671255982</v>
       </c>
       <c r="T14">
-        <v>0.6800704976487133</v>
+        <v>0.6861144942506393</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.12529022833472</v>
+        <v>11.1925755953859</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08591846743992704</v>
+        <v>0.08574296752406159</v>
       </c>
       <c r="C15">
-        <v>80.30588850297194</v>
+        <v>79.84560428995442</v>
       </c>
       <c r="D15">
-        <v>89.60788850297195</v>
+        <v>90.00160428995443</v>
       </c>
       <c r="E15">
-        <v>-35.898</v>
+        <v>-35.044</v>
       </c>
       <c r="F15">
-        <v>11.102</v>
+        <v>11.956</v>
       </c>
       <c r="G15">
         <v>1.8</v>
@@ -2505,28 +2505,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M15">
-        <v>0.5750836</v>
+        <v>0.6193208</v>
       </c>
       <c r="N15">
-        <v>5.861583066666666</v>
+        <v>5.817345866666667</v>
       </c>
       <c r="O15">
-        <v>1.465395766666667</v>
+        <v>1.454336466666667</v>
       </c>
       <c r="P15">
-        <v>4.396187299999999</v>
+        <v>4.3630094</v>
       </c>
       <c r="Q15">
-        <v>7.026187299999999</v>
+        <v>6.9930094</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09295168671255982</v>
+        <v>0.09337670642332743</v>
       </c>
       <c r="T15">
-        <v>0.6861144942506393</v>
+        <v>0.6922990489130753</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.1925755953859</v>
+        <v>10.39310591000119</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08574296752406159</v>
+        <v>0.08575871760819614</v>
       </c>
       <c r="C16">
-        <v>79.84560428995442</v>
+        <v>78.95612935670681</v>
       </c>
       <c r="D16">
-        <v>90.00160428995443</v>
+        <v>89.96612935670682</v>
       </c>
       <c r="E16">
-        <v>-35.044</v>
+        <v>-34.19</v>
       </c>
       <c r="F16">
-        <v>11.956</v>
+        <v>12.81</v>
       </c>
       <c r="G16">
         <v>1.8</v>
@@ -2587,45 +2587,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M16">
-        <v>0.6193208</v>
+        <v>0.6853350000000001</v>
       </c>
       <c r="N16">
-        <v>5.817345866666667</v>
+        <v>5.751331666666666</v>
       </c>
       <c r="O16">
-        <v>1.454336466666667</v>
+        <v>1.437832916666667</v>
       </c>
       <c r="P16">
-        <v>4.3630094</v>
+        <v>4.31349875</v>
       </c>
       <c r="Q16">
-        <v>6.9930094</v>
+        <v>6.94349875</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09337670642332743</v>
+        <v>0.09381172659787781</v>
       </c>
       <c r="T16">
-        <v>0.6922990489130753</v>
+        <v>0.6986291225087449</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.39310591000119</v>
+        <v>9.392000505835343</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08575871760819614</v>
+        <v>0.08559596769233069</v>
       </c>
       <c r="C17">
-        <v>78.95612935670681</v>
+        <v>78.47005557719086</v>
       </c>
       <c r="D17">
-        <v>89.96612935670682</v>
+        <v>90.33405557719087</v>
       </c>
       <c r="E17">
-        <v>-34.19</v>
+        <v>-33.336</v>
       </c>
       <c r="F17">
-        <v>12.81</v>
+        <v>13.664</v>
       </c>
       <c r="G17">
         <v>1.8</v>
@@ -2669,28 +2669,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M17">
-        <v>0.685335</v>
+        <v>0.7310240000000001</v>
       </c>
       <c r="N17">
-        <v>5.751331666666666</v>
+        <v>5.705642666666666</v>
       </c>
       <c r="O17">
-        <v>1.437832916666667</v>
+        <v>1.426410666666666</v>
       </c>
       <c r="P17">
-        <v>4.31349875</v>
+        <v>4.279231999999999</v>
       </c>
       <c r="Q17">
-        <v>6.94349875</v>
+        <v>6.909231999999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09381172659787781</v>
+        <v>0.09425710439563179</v>
       </c>
       <c r="T17">
-        <v>0.6986291225087449</v>
+        <v>0.7051099121424067</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.392000505835345</v>
+        <v>8.805000474220634</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08559596769233069</v>
+        <v>0.08543321777646526</v>
       </c>
       <c r="C18">
-        <v>78.47005557719086</v>
+        <v>77.98700350344531</v>
       </c>
       <c r="D18">
-        <v>90.33405557719087</v>
+        <v>90.70500350344531</v>
       </c>
       <c r="E18">
-        <v>-33.336</v>
+        <v>-32.482</v>
       </c>
       <c r="F18">
-        <v>13.664</v>
+        <v>14.518</v>
       </c>
       <c r="G18">
         <v>1.8</v>
@@ -2751,28 +2751,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M18">
-        <v>0.7310240000000001</v>
+        <v>0.7767130000000001</v>
       </c>
       <c r="N18">
-        <v>5.705642666666666</v>
+        <v>5.659953666666667</v>
       </c>
       <c r="O18">
-        <v>1.426410666666666</v>
+        <v>1.414988416666667</v>
       </c>
       <c r="P18">
-        <v>4.279231999999999</v>
+        <v>4.24496525</v>
       </c>
       <c r="Q18">
-        <v>6.909231999999999</v>
+        <v>6.87496525</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09425710439563179</v>
+        <v>0.09471321418851236</v>
       </c>
       <c r="T18">
-        <v>0.7051099121424067</v>
+        <v>0.7117468653816991</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.805000474220634</v>
+        <v>8.287059269854716</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08543321777646526</v>
+        <v>0.08527046786059982</v>
       </c>
       <c r="C19">
-        <v>77.98700350344531</v>
+        <v>77.50701051397525</v>
       </c>
       <c r="D19">
-        <v>90.70500350344531</v>
+        <v>91.07901051397525</v>
       </c>
       <c r="E19">
-        <v>-32.482</v>
+        <v>-31.628</v>
       </c>
       <c r="F19">
-        <v>14.518</v>
+        <v>15.372</v>
       </c>
       <c r="G19">
         <v>1.8</v>
@@ -2833,28 +2833,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M19">
-        <v>0.7767130000000001</v>
+        <v>0.8224020000000002</v>
       </c>
       <c r="N19">
-        <v>5.659953666666667</v>
+        <v>5.614264666666666</v>
       </c>
       <c r="O19">
-        <v>1.414988416666667</v>
+        <v>1.403566166666667</v>
       </c>
       <c r="P19">
-        <v>4.24496525</v>
+        <v>4.210698499999999</v>
       </c>
       <c r="Q19">
-        <v>6.87496525</v>
+        <v>6.840698499999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09471321418851236</v>
+        <v>0.09518044861048758</v>
       </c>
       <c r="T19">
-        <v>0.7117468653816991</v>
+        <v>0.7185456955292666</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.287059269854716</v>
+        <v>7.826667088196119</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08527046786059983</v>
+        <v>0.08522171794473439</v>
       </c>
       <c r="C20">
-        <v>77.5070105139752</v>
+        <v>76.76564117370161</v>
       </c>
       <c r="D20">
-        <v>91.07901051397521</v>
+        <v>91.19164117370161</v>
       </c>
       <c r="E20">
-        <v>-31.628</v>
+        <v>-30.774</v>
       </c>
       <c r="F20">
-        <v>15.372</v>
+        <v>16.226</v>
       </c>
       <c r="G20">
         <v>1.8</v>
@@ -2915,45 +2915,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M20">
-        <v>0.822402</v>
+        <v>0.8810718000000002</v>
       </c>
       <c r="N20">
-        <v>5.614264666666666</v>
+        <v>5.555594866666667</v>
       </c>
       <c r="O20">
-        <v>1.403566166666667</v>
+        <v>1.388898716666667</v>
       </c>
       <c r="P20">
-        <v>4.210698499999999</v>
+        <v>4.16669615</v>
       </c>
       <c r="Q20">
-        <v>6.840698499999999</v>
+        <v>6.79669615</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09518044861048758</v>
+        <v>0.09565921968485726</v>
       </c>
       <c r="T20">
-        <v>0.7185456955292666</v>
+        <v>0.7255123980261571</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.826667088196121</v>
+        <v>7.305496177118216</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08522171794473439</v>
+        <v>0.08506496802886893</v>
       </c>
       <c r="C21">
-        <v>76.76564117370161</v>
+        <v>76.27568787485012</v>
       </c>
       <c r="D21">
-        <v>91.19164117370161</v>
+        <v>91.55568787485012</v>
       </c>
       <c r="E21">
-        <v>-30.774</v>
+        <v>-29.92</v>
       </c>
       <c r="F21">
-        <v>16.226</v>
+        <v>17.08</v>
       </c>
       <c r="G21">
         <v>1.8</v>
@@ -2997,28 +2997,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M21">
-        <v>0.8810718000000002</v>
+        <v>0.9274440000000002</v>
       </c>
       <c r="N21">
-        <v>5.555594866666667</v>
+        <v>5.509222666666666</v>
       </c>
       <c r="O21">
-        <v>1.388898716666667</v>
+        <v>1.377305666666667</v>
       </c>
       <c r="P21">
-        <v>4.16669615</v>
+        <v>4.131917</v>
       </c>
       <c r="Q21">
-        <v>6.79669615</v>
+        <v>6.761917</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09565921968485726</v>
+        <v>0.09614996003608615</v>
       </c>
       <c r="T21">
-        <v>0.7255123980261571</v>
+        <v>0.7326532680854695</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.305496177118216</v>
+        <v>6.940221368262305</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08506496802886893</v>
+        <v>0.08490821811300348</v>
       </c>
       <c r="C22">
-        <v>76.27568787485012</v>
+        <v>75.78865285213232</v>
       </c>
       <c r="D22">
-        <v>91.55568787485012</v>
+        <v>91.92265285213233</v>
       </c>
       <c r="E22">
-        <v>-29.92</v>
+        <v>-29.066</v>
       </c>
       <c r="F22">
-        <v>17.08</v>
+        <v>17.934</v>
       </c>
       <c r="G22">
         <v>1.8</v>
@@ -3079,28 +3079,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M22">
-        <v>0.9274440000000002</v>
+        <v>0.9738162000000002</v>
       </c>
       <c r="N22">
-        <v>5.509222666666666</v>
+        <v>5.462850466666667</v>
       </c>
       <c r="O22">
-        <v>1.377305666666667</v>
+        <v>1.365712616666667</v>
       </c>
       <c r="P22">
-        <v>4.131917</v>
+        <v>4.09713785</v>
       </c>
       <c r="Q22">
-        <v>6.761917</v>
+        <v>6.72713785</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09614996003608615</v>
+        <v>0.09665312419367529</v>
       </c>
       <c r="T22">
-        <v>0.7326532680854695</v>
+        <v>0.739974919665271</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.940221368262305</v>
+        <v>6.60973463644029</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08490821811300348</v>
+        <v>0.08475146819713804</v>
       </c>
       <c r="C23">
-        <v>75.78865285213233</v>
+        <v>75.30457133704732</v>
       </c>
       <c r="D23">
-        <v>91.92265285213233</v>
+        <v>92.29257133704732</v>
       </c>
       <c r="E23">
-        <v>-29.066</v>
+        <v>-28.212</v>
       </c>
       <c r="F23">
-        <v>17.934</v>
+        <v>18.788</v>
       </c>
       <c r="G23">
         <v>1.8</v>
@@ -3161,28 +3161,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M23">
-        <v>0.9738162</v>
+        <v>1.0201884</v>
       </c>
       <c r="N23">
-        <v>5.462850466666667</v>
+        <v>5.416478266666666</v>
       </c>
       <c r="O23">
-        <v>1.365712616666667</v>
+        <v>1.354119566666667</v>
       </c>
       <c r="P23">
-        <v>4.09713785</v>
+        <v>4.0623587</v>
       </c>
       <c r="Q23">
-        <v>6.72713785</v>
+        <v>6.6923587</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09665312419367529</v>
+        <v>0.09716918999633081</v>
       </c>
       <c r="T23">
-        <v>0.739974919665271</v>
+        <v>0.7474843059009648</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.609734636440292</v>
+        <v>6.309292152965733</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08475146819713804</v>
+        <v>0.08476721828127258</v>
       </c>
       <c r="C24">
-        <v>75.30457133704732</v>
+        <v>74.41326778222185</v>
       </c>
       <c r="D24">
-        <v>92.29257133704732</v>
+        <v>92.25526778222185</v>
       </c>
       <c r="E24">
-        <v>-28.212</v>
+        <v>-27.358</v>
       </c>
       <c r="F24">
-        <v>18.788</v>
+        <v>19.642</v>
       </c>
       <c r="G24">
         <v>1.8</v>
@@ -3243,45 +3243,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M24">
-        <v>1.0201884</v>
+        <v>1.0862026</v>
       </c>
       <c r="N24">
-        <v>5.416478266666666</v>
+        <v>5.350464066666667</v>
       </c>
       <c r="O24">
-        <v>1.354119566666667</v>
+        <v>1.337616016666667</v>
       </c>
       <c r="P24">
-        <v>4.0623587</v>
+        <v>4.01284805</v>
       </c>
       <c r="Q24">
-        <v>6.6923587</v>
+        <v>6.64284805</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09716918999633081</v>
+        <v>0.09769866010554881</v>
       </c>
       <c r="T24">
-        <v>0.7474843059009648</v>
+        <v>0.7551887411297936</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.309292152965733</v>
+        <v>5.925843545823463</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08476721828127258</v>
+        <v>0.08461796836540715</v>
       </c>
       <c r="C25">
-        <v>74.41326778222185</v>
+        <v>73.9139769938175</v>
       </c>
       <c r="D25">
-        <v>92.25526778222185</v>
+        <v>92.60997699381751</v>
       </c>
       <c r="E25">
-        <v>-27.358</v>
+        <v>-26.504</v>
       </c>
       <c r="F25">
-        <v>19.642</v>
+        <v>20.496</v>
       </c>
       <c r="G25">
         <v>1.8</v>
@@ -3325,28 +3325,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M25">
-        <v>1.0862026</v>
+        <v>1.1334288</v>
       </c>
       <c r="N25">
-        <v>5.350464066666667</v>
+        <v>5.303237866666667</v>
       </c>
       <c r="O25">
-        <v>1.337616016666667</v>
+        <v>1.325809466666667</v>
       </c>
       <c r="P25">
-        <v>4.01284805</v>
+        <v>3.9774284</v>
       </c>
       <c r="Q25">
-        <v>6.64284805</v>
+        <v>6.6074284</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09769866010554881</v>
+        <v>0.09824206363869362</v>
       </c>
       <c r="T25">
-        <v>0.7551887411297936</v>
+        <v>0.7630959246541179</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.925843545823463</v>
+        <v>5.67893339808082</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08461796836540715</v>
+        <v>0.08446871844954169</v>
       </c>
       <c r="C26">
-        <v>73.9139769938175</v>
+        <v>73.41742435253113</v>
       </c>
       <c r="D26">
-        <v>92.60997699381751</v>
+        <v>92.96742435253113</v>
       </c>
       <c r="E26">
-        <v>-26.504</v>
+        <v>-25.65</v>
       </c>
       <c r="F26">
-        <v>20.496</v>
+        <v>21.35</v>
       </c>
       <c r="G26">
         <v>1.8</v>
@@ -3407,28 +3407,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M26">
-        <v>1.1334288</v>
+        <v>1.180655</v>
       </c>
       <c r="N26">
-        <v>5.303237866666667</v>
+        <v>5.256011666666667</v>
       </c>
       <c r="O26">
-        <v>1.325809466666667</v>
+        <v>1.314002916666667</v>
       </c>
       <c r="P26">
-        <v>3.9774284</v>
+        <v>3.94200875</v>
       </c>
       <c r="Q26">
-        <v>6.6074284</v>
+        <v>6.57200875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09824206363869362</v>
+        <v>0.09879995793272227</v>
       </c>
       <c r="T26">
-        <v>0.7630959246541179</v>
+        <v>0.7712139664057573</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.67893339808082</v>
+        <v>5.451776062157587</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08446871844954169</v>
+        <v>0.08431946853367625</v>
       </c>
       <c r="C27">
-        <v>73.41742435253113</v>
+        <v>72.92364168654527</v>
       </c>
       <c r="D27">
-        <v>92.96742435253113</v>
+        <v>93.32764168654528</v>
       </c>
       <c r="E27">
-        <v>-25.65</v>
+        <v>-24.796</v>
       </c>
       <c r="F27">
-        <v>21.35</v>
+        <v>22.204</v>
       </c>
       <c r="G27">
         <v>1.8</v>
@@ -3489,28 +3489,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M27">
-        <v>1.180655</v>
+        <v>1.2278812</v>
       </c>
       <c r="N27">
-        <v>5.256011666666667</v>
+        <v>5.208785466666667</v>
       </c>
       <c r="O27">
-        <v>1.314002916666667</v>
+        <v>1.302196366666667</v>
       </c>
       <c r="P27">
-        <v>3.94200875</v>
+        <v>3.9065891</v>
       </c>
       <c r="Q27">
-        <v>6.57200875</v>
+        <v>6.5365891</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09879995793272227</v>
+        <v>0.09937293045091386</v>
       </c>
       <c r="T27">
-        <v>0.7712139664057573</v>
+        <v>0.7795514146912251</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.451776062157587</v>
+        <v>5.242092367459219</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08431946853367625</v>
+        <v>0.08417021861781082</v>
       </c>
       <c r="C28">
-        <v>72.92364168654527</v>
+        <v>72.43266131925513</v>
       </c>
       <c r="D28">
-        <v>93.32764168654528</v>
+        <v>93.69066131925514</v>
       </c>
       <c r="E28">
-        <v>-24.796</v>
+        <v>-23.942</v>
       </c>
       <c r="F28">
-        <v>22.204</v>
+        <v>23.058</v>
       </c>
       <c r="G28">
         <v>1.8</v>
@@ -3571,28 +3571,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M28">
-        <v>1.2278812</v>
+        <v>1.2751074</v>
       </c>
       <c r="N28">
-        <v>5.208785466666667</v>
+        <v>5.161559266666666</v>
       </c>
       <c r="O28">
-        <v>1.302196366666667</v>
+        <v>1.290389816666667</v>
       </c>
       <c r="P28">
-        <v>3.9065891</v>
+        <v>3.87116945</v>
       </c>
       <c r="Q28">
-        <v>6.5365891</v>
+        <v>6.501169449999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09937293045091386</v>
+        <v>0.0999616008463162</v>
       </c>
       <c r="T28">
-        <v>0.7795514146912251</v>
+        <v>0.7881172862173905</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.242092367459219</v>
+        <v>5.047940798294062</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08417021861781082</v>
+        <v>0.08402096870194536</v>
       </c>
       <c r="C29">
-        <v>72.43266131925513</v>
+        <v>71.94451607893753</v>
       </c>
       <c r="D29">
-        <v>93.69066131925514</v>
+        <v>94.05651607893753</v>
       </c>
       <c r="E29">
-        <v>-23.942</v>
+        <v>-23.088</v>
       </c>
       <c r="F29">
-        <v>23.058</v>
+        <v>23.912</v>
       </c>
       <c r="G29">
         <v>1.8</v>
@@ -3653,28 +3653,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M29">
-        <v>1.2751074</v>
+        <v>1.3223336</v>
       </c>
       <c r="N29">
-        <v>5.161559266666666</v>
+        <v>5.114333066666666</v>
       </c>
       <c r="O29">
-        <v>1.290389816666667</v>
+        <v>1.278583266666667</v>
       </c>
       <c r="P29">
-        <v>3.87116945</v>
+        <v>3.835749799999999</v>
       </c>
       <c r="Q29">
-        <v>6.501169449999999</v>
+        <v>6.465749799999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0999616008463162</v>
+        <v>0.1005666231971463</v>
       </c>
       <c r="T29">
-        <v>0.7881172862173905</v>
+        <v>0.7969210986192827</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.047940798294062</v>
+        <v>4.867657198354989</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08402096870194536</v>
+        <v>0.08387171878607992</v>
       </c>
       <c r="C30">
-        <v>71.94451607893753</v>
+        <v>71.45923930864656</v>
       </c>
       <c r="D30">
-        <v>94.05651607893753</v>
+        <v>94.42523930864657</v>
       </c>
       <c r="E30">
-        <v>-23.088</v>
+        <v>-22.23399999999999</v>
       </c>
       <c r="F30">
-        <v>23.912</v>
+        <v>24.76600000000001</v>
       </c>
       <c r="G30">
         <v>1.8</v>
@@ -3735,28 +3735,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M30">
-        <v>1.3223336</v>
+        <v>1.3695598</v>
       </c>
       <c r="N30">
-        <v>5.114333066666666</v>
+        <v>5.067106866666666</v>
       </c>
       <c r="O30">
-        <v>1.278583266666667</v>
+        <v>1.266776716666667</v>
       </c>
       <c r="P30">
-        <v>3.835749799999999</v>
+        <v>3.80033015</v>
       </c>
       <c r="Q30">
-        <v>6.465749799999999</v>
+        <v>6.43033015</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1005666231971463</v>
+        <v>0.1011886884310985</v>
       </c>
       <c r="T30">
-        <v>0.7969210986192827</v>
+        <v>0.8059729057367211</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.867657198354989</v>
+        <v>4.69980695013585</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08387171878607992</v>
+        <v>0.08372246887021448</v>
       </c>
       <c r="C31">
-        <v>71.45923930864657</v>
+        <v>70.97686487634424</v>
       </c>
       <c r="D31">
-        <v>94.42523930864657</v>
+        <v>94.79686487634424</v>
       </c>
       <c r="E31">
-        <v>-22.234</v>
+        <v>-21.38</v>
       </c>
       <c r="F31">
-        <v>24.766</v>
+        <v>25.62</v>
       </c>
       <c r="G31">
         <v>1.8</v>
@@ -3817,28 +3817,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M31">
-        <v>1.3695598</v>
+        <v>1.416786</v>
       </c>
       <c r="N31">
-        <v>5.067106866666666</v>
+        <v>5.019880666666666</v>
       </c>
       <c r="O31">
-        <v>1.266776716666667</v>
+        <v>1.254970166666667</v>
       </c>
       <c r="P31">
-        <v>3.80033015</v>
+        <v>3.7649105</v>
       </c>
       <c r="Q31">
-        <v>6.43033015</v>
+        <v>6.3949105</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1011886884310985</v>
+        <v>0.1018285269574493</v>
       </c>
       <c r="T31">
-        <v>0.8059729057367211</v>
+        <v>0.8152833359146578</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.699806950135851</v>
+        <v>4.543146718464656</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08372246887021448</v>
+        <v>0.08415446895434903</v>
       </c>
       <c r="C32">
-        <v>70.97686487634424</v>
+        <v>69.05513392559072</v>
       </c>
       <c r="D32">
-        <v>94.79686487634424</v>
+        <v>93.72913392559073</v>
       </c>
       <c r="E32">
-        <v>-21.38</v>
+        <v>-20.526</v>
       </c>
       <c r="F32">
-        <v>25.62</v>
+        <v>26.474</v>
       </c>
       <c r="G32">
         <v>1.8</v>
@@ -3899,45 +3899,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M32">
-        <v>1.416786</v>
+        <v>1.5301972</v>
       </c>
       <c r="N32">
-        <v>5.019880666666666</v>
+        <v>4.906469466666667</v>
       </c>
       <c r="O32">
-        <v>1.254970166666667</v>
+        <v>1.226617366666667</v>
       </c>
       <c r="P32">
-        <v>3.7649105</v>
+        <v>3.6798521</v>
       </c>
       <c r="Q32">
-        <v>6.3949105</v>
+        <v>6.3098521</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1018285269574493</v>
+        <v>0.1024869115280421</v>
       </c>
       <c r="T32">
-        <v>0.8152833359146578</v>
+        <v>0.824863633633984</v>
       </c>
       <c r="U32">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.543146718464656</v>
+        <v>4.206429515533467</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08415446895434903</v>
+        <v>0.08402396903848358</v>
       </c>
       <c r="C33">
-        <v>69.05513392559072</v>
+        <v>68.52113324536613</v>
       </c>
       <c r="D33">
-        <v>93.72913392559073</v>
+        <v>94.04913324536614</v>
       </c>
       <c r="E33">
-        <v>-20.526</v>
+        <v>-19.672</v>
       </c>
       <c r="F33">
-        <v>26.474</v>
+        <v>27.328</v>
       </c>
       <c r="G33">
         <v>1.8</v>
@@ -3981,28 +3981,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M33">
-        <v>1.5301972</v>
+        <v>1.5795584</v>
       </c>
       <c r="N33">
-        <v>4.906469466666667</v>
+        <v>4.857108266666666</v>
       </c>
       <c r="O33">
-        <v>1.226617366666667</v>
+        <v>1.214277066666666</v>
       </c>
       <c r="P33">
-        <v>3.6798521</v>
+        <v>3.642831199999999</v>
       </c>
       <c r="Q33">
-        <v>6.3098521</v>
+        <v>6.272831199999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1024869115280421</v>
+        <v>0.1031646603507112</v>
       </c>
       <c r="T33">
-        <v>0.824863633633984</v>
+        <v>0.8347257048156433</v>
       </c>
       <c r="U33">
         <v>0.0578</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.206429515533467</v>
+        <v>4.074978593173045</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08402396903848358</v>
+        <v>0.08475971912261815</v>
       </c>
       <c r="C34">
-        <v>68.52113324536613</v>
+        <v>65.89102553061906</v>
       </c>
       <c r="D34">
-        <v>94.04913324536614</v>
+        <v>92.27302553061907</v>
       </c>
       <c r="E34">
-        <v>-19.672</v>
+        <v>-18.818</v>
       </c>
       <c r="F34">
-        <v>27.328</v>
+        <v>28.182</v>
       </c>
       <c r="G34">
         <v>1.8</v>
@@ -4063,45 +4063,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M34">
-        <v>1.5795584</v>
+        <v>1.7275566</v>
       </c>
       <c r="N34">
-        <v>4.857108266666666</v>
+        <v>4.709110066666666</v>
       </c>
       <c r="O34">
-        <v>1.214277066666666</v>
+        <v>1.177277516666666</v>
       </c>
       <c r="P34">
-        <v>3.642831199999999</v>
+        <v>3.531832549999999</v>
       </c>
       <c r="Q34">
-        <v>6.272831199999999</v>
+        <v>6.16183255</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1031646603507112</v>
+        <v>0.1038626404815196</v>
       </c>
       <c r="T34">
-        <v>0.8347257048156433</v>
+        <v>0.8448821661818299</v>
       </c>
       <c r="U34">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.074978593173045</v>
+        <v>3.7258788896796</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08475971912261815</v>
+        <v>0.08465546920675271</v>
       </c>
       <c r="C35">
-        <v>65.89102553061906</v>
+        <v>65.28459570142387</v>
       </c>
       <c r="D35">
-        <v>92.27302553061907</v>
+        <v>92.52059570142387</v>
       </c>
       <c r="E35">
-        <v>-18.818</v>
+        <v>-17.964</v>
       </c>
       <c r="F35">
-        <v>28.182</v>
+        <v>29.036</v>
       </c>
       <c r="G35">
         <v>1.8</v>
@@ -4145,28 +4145,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M35">
-        <v>1.7275566</v>
+        <v>1.7799068</v>
       </c>
       <c r="N35">
-        <v>4.709110066666666</v>
+        <v>4.656759866666667</v>
       </c>
       <c r="O35">
-        <v>1.177277516666666</v>
+        <v>1.164189966666667</v>
       </c>
       <c r="P35">
-        <v>3.531832549999999</v>
+        <v>3.4925699</v>
       </c>
       <c r="Q35">
-        <v>6.16183255</v>
+        <v>6.1225699</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1038626404815196</v>
+        <v>0.1045817715253829</v>
       </c>
       <c r="T35">
-        <v>0.8448821661818299</v>
+        <v>0.8553463991045673</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.7258788896796</v>
+        <v>3.61629421645373</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08465546920675271</v>
+        <v>0.08455121929088726</v>
       </c>
       <c r="C36">
-        <v>65.28459570142387</v>
+        <v>64.67949791648174</v>
       </c>
       <c r="D36">
-        <v>92.52059570142387</v>
+        <v>92.76949791648174</v>
       </c>
       <c r="E36">
-        <v>-17.964</v>
+        <v>-17.11</v>
       </c>
       <c r="F36">
-        <v>29.036</v>
+        <v>29.89</v>
       </c>
       <c r="G36">
         <v>1.8</v>
@@ -4227,28 +4227,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M36">
-        <v>1.7799068</v>
+        <v>1.832257</v>
       </c>
       <c r="N36">
-        <v>4.656759866666667</v>
+        <v>4.604409666666666</v>
       </c>
       <c r="O36">
-        <v>1.164189966666667</v>
+        <v>1.151102416666667</v>
       </c>
       <c r="P36">
-        <v>3.4925699</v>
+        <v>3.45330725</v>
       </c>
       <c r="Q36">
-        <v>6.1225699</v>
+        <v>6.08330725</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1045817715253829</v>
+        <v>0.1053230296782881</v>
       </c>
       <c r="T36">
-        <v>0.8553463991045673</v>
+        <v>0.8661326084249276</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.61629421645373</v>
+        <v>3.512971524555052</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08455121929088726</v>
+        <v>0.08520296937502181</v>
       </c>
       <c r="C37">
-        <v>64.67949791648174</v>
+        <v>62.29103163053438</v>
       </c>
       <c r="D37">
-        <v>92.76949791648174</v>
+        <v>91.23503163053439</v>
       </c>
       <c r="E37">
-        <v>-17.11</v>
+        <v>-16.25599999999999</v>
       </c>
       <c r="F37">
-        <v>29.89</v>
+        <v>30.74400000000001</v>
       </c>
       <c r="G37">
         <v>1.8</v>
@@ -4309,45 +4309,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M37">
-        <v>1.832257</v>
+        <v>1.970690400000001</v>
       </c>
       <c r="N37">
-        <v>4.604409666666666</v>
+        <v>4.465976266666666</v>
       </c>
       <c r="O37">
-        <v>1.151102416666667</v>
+        <v>1.116494066666667</v>
       </c>
       <c r="P37">
-        <v>3.45330725</v>
+        <v>3.3494822</v>
       </c>
       <c r="Q37">
-        <v>6.08330725</v>
+        <v>5.9794822</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1053230296782881</v>
+        <v>0.1060874521484716</v>
       </c>
       <c r="T37">
-        <v>0.8661326084249276</v>
+        <v>0.8772558867865491</v>
       </c>
       <c r="U37">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.512971524555052</v>
+        <v>3.266198823857195</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08520296937502182</v>
+        <v>0.08511971945915638</v>
       </c>
       <c r="C38">
-        <v>62.29103163053435</v>
+        <v>61.63019955776518</v>
       </c>
       <c r="D38">
-        <v>91.23503163053435</v>
+        <v>91.42819955776518</v>
       </c>
       <c r="E38">
-        <v>-16.256</v>
+        <v>-15.402</v>
       </c>
       <c r="F38">
-        <v>30.744</v>
+        <v>31.598</v>
       </c>
       <c r="G38">
         <v>1.8</v>
@@ -4391,28 +4391,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M38">
-        <v>1.9706904</v>
+        <v>2.0254318</v>
       </c>
       <c r="N38">
-        <v>4.465976266666667</v>
+        <v>4.411234866666666</v>
       </c>
       <c r="O38">
-        <v>1.116494066666667</v>
+        <v>1.102808716666666</v>
       </c>
       <c r="P38">
-        <v>3.3494822</v>
+        <v>3.308426149999999</v>
       </c>
       <c r="Q38">
-        <v>5.9794822</v>
+        <v>5.93842615</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1060874521484716</v>
+        <v>0.1068761419986609</v>
       </c>
       <c r="T38">
-        <v>0.8772558867865491</v>
+        <v>0.8887322850961585</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.266198823857196</v>
+        <v>3.177923179969163</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08511971945915638</v>
+        <v>0.08503646954329093</v>
       </c>
       <c r="C39">
-        <v>61.63019955776518</v>
+        <v>60.97018719247108</v>
       </c>
       <c r="D39">
-        <v>91.42819955776518</v>
+        <v>91.62218719247109</v>
       </c>
       <c r="E39">
-        <v>-15.402</v>
+        <v>-14.54799999999999</v>
       </c>
       <c r="F39">
-        <v>31.598</v>
+        <v>32.45200000000001</v>
       </c>
       <c r="G39">
         <v>1.8</v>
@@ -4473,28 +4473,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M39">
-        <v>2.0254318</v>
+        <v>2.0801732</v>
       </c>
       <c r="N39">
-        <v>4.411234866666666</v>
+        <v>4.356493466666667</v>
       </c>
       <c r="O39">
-        <v>1.102808716666666</v>
+        <v>1.089123366666667</v>
       </c>
       <c r="P39">
-        <v>3.308426149999999</v>
+        <v>3.2673701</v>
       </c>
       <c r="Q39">
-        <v>5.93842615</v>
+        <v>5.8973701</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1068761419986609</v>
+        <v>0.1076902734569208</v>
       </c>
       <c r="T39">
-        <v>0.8887322850961585</v>
+        <v>0.9005788898028522</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.177923179969163</v>
+        <v>3.094293622601553</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08503646954329093</v>
+        <v>0.0849532196274255</v>
       </c>
       <c r="C40">
-        <v>60.97018719247108</v>
+        <v>60.31099976338511</v>
       </c>
       <c r="D40">
-        <v>91.62218719247109</v>
+        <v>91.81699976338511</v>
       </c>
       <c r="E40">
-        <v>-14.54799999999999</v>
+        <v>-13.694</v>
       </c>
       <c r="F40">
-        <v>32.45200000000001</v>
+        <v>33.306</v>
       </c>
       <c r="G40">
         <v>1.8</v>
@@ -4555,28 +4555,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M40">
-        <v>2.0801732</v>
+        <v>2.134914600000001</v>
       </c>
       <c r="N40">
-        <v>4.356493466666667</v>
+        <v>4.301752066666666</v>
       </c>
       <c r="O40">
-        <v>1.089123366666667</v>
+        <v>1.075438016666666</v>
       </c>
       <c r="P40">
-        <v>3.2673701</v>
+        <v>3.226314049999999</v>
       </c>
       <c r="Q40">
-        <v>5.8973701</v>
+        <v>5.856314049999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1076902734569208</v>
+        <v>0.1085310977498778</v>
       </c>
       <c r="T40">
-        <v>0.9005788898028522</v>
+        <v>0.9128139077786178</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.094293622601553</v>
+        <v>3.014952760483564</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0849532196274255</v>
+        <v>0.08720996971156005</v>
       </c>
       <c r="C41">
-        <v>60.31099976338511</v>
+        <v>54.45318007010105</v>
       </c>
       <c r="D41">
-        <v>91.81699976338511</v>
+        <v>86.81318007010105</v>
       </c>
       <c r="E41">
-        <v>-13.694</v>
+        <v>-12.84</v>
       </c>
       <c r="F41">
-        <v>33.306</v>
+        <v>34.16</v>
       </c>
       <c r="G41">
         <v>1.8</v>
@@ -4637,45 +4637,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M41">
-        <v>2.134914600000001</v>
+        <v>2.456104</v>
       </c>
       <c r="N41">
-        <v>4.301752066666666</v>
+        <v>3.980562666666666</v>
       </c>
       <c r="O41">
-        <v>1.075438016666666</v>
+        <v>0.9951406666666666</v>
       </c>
       <c r="P41">
-        <v>3.226314049999999</v>
+        <v>2.985422</v>
       </c>
       <c r="Q41">
-        <v>5.856314049999999</v>
+        <v>5.615422</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1085310977498778</v>
+        <v>0.1093999495192667</v>
       </c>
       <c r="T41">
-        <v>0.9128139077786178</v>
+        <v>0.9254567596869089</v>
       </c>
       <c r="U41">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.014952760483564</v>
+        <v>2.620681643231177</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08720996971156005</v>
+        <v>0.08718521979569459</v>
       </c>
       <c r="C42">
-        <v>54.45318007010105</v>
+        <v>53.65109761248345</v>
       </c>
       <c r="D42">
-        <v>86.81318007010105</v>
+        <v>86.86509761248345</v>
       </c>
       <c r="E42">
-        <v>-12.84</v>
+        <v>-11.986</v>
       </c>
       <c r="F42">
-        <v>34.16</v>
+        <v>35.014</v>
       </c>
       <c r="G42">
         <v>1.8</v>
@@ -4719,28 +4719,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M42">
-        <v>2.456104</v>
+        <v>2.5175066</v>
       </c>
       <c r="N42">
-        <v>3.980562666666666</v>
+        <v>3.919160066666666</v>
       </c>
       <c r="O42">
-        <v>0.9951406666666666</v>
+        <v>0.9797900166666665</v>
       </c>
       <c r="P42">
-        <v>2.985422</v>
+        <v>2.93937005</v>
       </c>
       <c r="Q42">
-        <v>5.615422</v>
+        <v>5.56937005</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1093999495192667</v>
+        <v>0.1102982538910078</v>
       </c>
       <c r="T42">
-        <v>0.9254567596869089</v>
+        <v>0.9385281828463286</v>
       </c>
       <c r="U42">
         <v>0.07190000000000001</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.620681643231177</v>
+        <v>2.556762578762124</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08718521979569459</v>
+        <v>0.08838896987982915</v>
       </c>
       <c r="C43">
-        <v>53.65109761248345</v>
+        <v>50.34191100302972</v>
       </c>
       <c r="D43">
-        <v>86.86509761248345</v>
+        <v>84.40991100302973</v>
       </c>
       <c r="E43">
-        <v>-11.986</v>
+        <v>-11.13199999999999</v>
       </c>
       <c r="F43">
-        <v>35.014</v>
+        <v>35.86800000000001</v>
       </c>
       <c r="G43">
         <v>1.8</v>
@@ -4801,45 +4801,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M43">
-        <v>2.5175066</v>
+        <v>2.718794400000001</v>
       </c>
       <c r="N43">
-        <v>3.919160066666666</v>
+        <v>3.717872266666665</v>
       </c>
       <c r="O43">
-        <v>0.9797900166666665</v>
+        <v>0.9294680666666664</v>
       </c>
       <c r="P43">
-        <v>2.93937005</v>
+        <v>2.788404199999999</v>
       </c>
       <c r="Q43">
-        <v>5.56937005</v>
+        <v>5.418404199999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1102982538910078</v>
+        <v>0.1112275342755675</v>
       </c>
       <c r="T43">
-        <v>0.9385281828463286</v>
+        <v>0.9520503447353833</v>
       </c>
       <c r="U43">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.556762578762124</v>
+        <v>2.367470915294906</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08838896987982917</v>
+        <v>0.08839346996396369</v>
       </c>
       <c r="C44">
-        <v>50.34191100302969</v>
+        <v>49.47899292939956</v>
       </c>
       <c r="D44">
-        <v>84.40991100302969</v>
+        <v>84.40099292939956</v>
       </c>
       <c r="E44">
-        <v>-11.132</v>
+        <v>-10.278</v>
       </c>
       <c r="F44">
-        <v>35.868</v>
+        <v>36.722</v>
       </c>
       <c r="G44">
         <v>1.8</v>
@@ -4883,28 +4883,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M44">
-        <v>2.7187944</v>
+        <v>2.7835276</v>
       </c>
       <c r="N44">
-        <v>3.717872266666666</v>
+        <v>3.653139066666666</v>
       </c>
       <c r="O44">
-        <v>0.9294680666666666</v>
+        <v>0.9132847666666666</v>
       </c>
       <c r="P44">
-        <v>2.7884042</v>
+        <v>2.7398543</v>
       </c>
       <c r="Q44">
-        <v>5.418404199999999</v>
+        <v>5.3698543</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1112275342755675</v>
+        <v>0.11218942098941</v>
       </c>
       <c r="T44">
-        <v>0.9520503447353833</v>
+        <v>0.9660469684451065</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.367470915294906</v>
+        <v>2.312413452148514</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08839346996396369</v>
+        <v>0.08839797004809827</v>
       </c>
       <c r="C45">
-        <v>49.47899292939956</v>
+        <v>48.61607673999439</v>
       </c>
       <c r="D45">
-        <v>84.40099292939956</v>
+        <v>84.39207673999439</v>
       </c>
       <c r="E45">
-        <v>-10.278</v>
+        <v>-9.423999999999999</v>
       </c>
       <c r="F45">
-        <v>36.722</v>
+        <v>37.576</v>
       </c>
       <c r="G45">
         <v>1.8</v>
@@ -4965,28 +4965,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M45">
-        <v>2.7835276</v>
+        <v>2.8482608</v>
       </c>
       <c r="N45">
-        <v>3.653139066666666</v>
+        <v>3.588405866666666</v>
       </c>
       <c r="O45">
-        <v>0.9132847666666666</v>
+        <v>0.8971014666666666</v>
       </c>
       <c r="P45">
-        <v>2.7398543</v>
+        <v>2.6913044</v>
       </c>
       <c r="Q45">
-        <v>5.3698543</v>
+        <v>5.3213044</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.11218942098941</v>
+        <v>0.1131856608001755</v>
       </c>
       <c r="T45">
-        <v>0.9660469684451065</v>
+        <v>0.9805434715730345</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.312413452148514</v>
+        <v>2.259858600963319</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08839797004809827</v>
+        <v>0.08840247013223282</v>
       </c>
       <c r="C46">
-        <v>48.61607673999439</v>
+        <v>47.75316243421729</v>
       </c>
       <c r="D46">
-        <v>84.39207673999439</v>
+        <v>84.3831624342173</v>
       </c>
       <c r="E46">
-        <v>-9.423999999999999</v>
+        <v>-8.569999999999993</v>
       </c>
       <c r="F46">
-        <v>37.576</v>
+        <v>38.43000000000001</v>
       </c>
       <c r="G46">
         <v>1.8</v>
@@ -5047,28 +5047,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M46">
-        <v>2.8482608</v>
+        <v>2.912994000000001</v>
       </c>
       <c r="N46">
-        <v>3.588405866666666</v>
+        <v>3.523672666666666</v>
       </c>
       <c r="O46">
-        <v>0.8971014666666666</v>
+        <v>0.8809181666666664</v>
       </c>
       <c r="P46">
-        <v>2.6913044</v>
+        <v>2.642754499999999</v>
       </c>
       <c r="Q46">
-        <v>5.3213044</v>
+        <v>5.2727545</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1131856608001755</v>
+        <v>0.1142181275131506</v>
       </c>
       <c r="T46">
-        <v>0.9805434715730345</v>
+        <v>0.9955671202692504</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.259858600963319</v>
+        <v>2.209639520941912</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08840247013223282</v>
+        <v>0.08840697021636737</v>
       </c>
       <c r="C47">
-        <v>47.75316243421729</v>
+        <v>46.8902500114713</v>
       </c>
       <c r="D47">
-        <v>84.3831624342173</v>
+        <v>84.3742500114713</v>
       </c>
       <c r="E47">
-        <v>-8.569999999999993</v>
+        <v>-7.715999999999994</v>
       </c>
       <c r="F47">
-        <v>38.43000000000001</v>
+        <v>39.28400000000001</v>
       </c>
       <c r="G47">
         <v>1.8</v>
@@ -5129,28 +5129,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M47">
-        <v>2.912994000000001</v>
+        <v>2.977727200000001</v>
       </c>
       <c r="N47">
-        <v>3.523672666666666</v>
+        <v>3.458939466666666</v>
       </c>
       <c r="O47">
-        <v>0.8809181666666664</v>
+        <v>0.8647348666666664</v>
       </c>
       <c r="P47">
-        <v>2.642754499999999</v>
+        <v>2.594204599999999</v>
       </c>
       <c r="Q47">
-        <v>5.2727545</v>
+        <v>5.224204599999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1142181275131506</v>
+        <v>0.1152888337340136</v>
       </c>
       <c r="T47">
-        <v>0.9955671202692504</v>
+        <v>1.01114720039866</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.209639520941912</v>
+        <v>2.161603879182306</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08840697021636737</v>
+        <v>0.08841147030050192</v>
       </c>
       <c r="C48">
-        <v>46.8902500114713</v>
+        <v>46.02733947115988</v>
       </c>
       <c r="D48">
-        <v>84.3742500114713</v>
+        <v>84.36533947115988</v>
       </c>
       <c r="E48">
-        <v>-7.715999999999994</v>
+        <v>-6.861999999999995</v>
       </c>
       <c r="F48">
-        <v>39.28400000000001</v>
+        <v>40.13800000000001</v>
       </c>
       <c r="G48">
         <v>1.8</v>
@@ -5211,28 +5211,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M48">
-        <v>2.977727200000001</v>
+        <v>3.042460400000001</v>
       </c>
       <c r="N48">
-        <v>3.458939466666666</v>
+        <v>3.394206266666666</v>
       </c>
       <c r="O48">
-        <v>0.8647348666666664</v>
+        <v>0.8485515666666664</v>
       </c>
       <c r="P48">
-        <v>2.594204599999999</v>
+        <v>2.545654699999999</v>
       </c>
       <c r="Q48">
-        <v>5.224204599999999</v>
+        <v>5.175654699999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1152888337340136</v>
+        <v>0.1163999439632112</v>
       </c>
       <c r="T48">
-        <v>1.01114720039866</v>
+        <v>1.027315208080122</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.161603879182306</v>
+        <v>2.11561230728481</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08841147030050192</v>
+        <v>0.08841597038463649</v>
       </c>
       <c r="C49">
-        <v>46.02733947115988</v>
+        <v>45.16443081268666</v>
       </c>
       <c r="D49">
-        <v>84.36533947115988</v>
+        <v>84.35643081268667</v>
       </c>
       <c r="E49">
-        <v>-6.861999999999995</v>
+        <v>-6.007999999999996</v>
       </c>
       <c r="F49">
-        <v>40.13800000000001</v>
+        <v>40.992</v>
       </c>
       <c r="G49">
         <v>1.8</v>
@@ -5293,28 +5293,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M49">
-        <v>3.042460400000001</v>
+        <v>3.1071936</v>
       </c>
       <c r="N49">
-        <v>3.394206266666666</v>
+        <v>3.329473066666666</v>
       </c>
       <c r="O49">
-        <v>0.8485515666666664</v>
+        <v>0.8323682666666665</v>
       </c>
       <c r="P49">
-        <v>2.545654699999999</v>
+        <v>2.4971048</v>
       </c>
       <c r="Q49">
-        <v>5.175654699999999</v>
+        <v>5.1271048</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1163999439632112</v>
+        <v>0.117553789201224</v>
       </c>
       <c r="T49">
-        <v>1.027315208080122</v>
+        <v>1.044105062210872</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.11561230728481</v>
+        <v>2.071537050883043</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08841597038463649</v>
+        <v>0.08842047046877104</v>
       </c>
       <c r="C50">
-        <v>45.16443081268666</v>
+        <v>44.30152403545563</v>
       </c>
       <c r="D50">
-        <v>84.35643081268667</v>
+        <v>84.34752403545563</v>
       </c>
       <c r="E50">
-        <v>-6.007999999999996</v>
+        <v>-5.153999999999996</v>
       </c>
       <c r="F50">
-        <v>40.992</v>
+        <v>41.846</v>
       </c>
       <c r="G50">
         <v>1.8</v>
@@ -5375,28 +5375,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M50">
-        <v>3.1071936</v>
+        <v>3.1719268</v>
       </c>
       <c r="N50">
-        <v>3.329473066666666</v>
+        <v>3.264739866666666</v>
       </c>
       <c r="O50">
-        <v>0.8323682666666665</v>
+        <v>0.8161849666666665</v>
       </c>
       <c r="P50">
-        <v>2.4971048</v>
+        <v>2.4485549</v>
       </c>
       <c r="Q50">
-        <v>5.1271048</v>
+        <v>5.078554899999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.117553789201224</v>
+        <v>0.1187528832721001</v>
       </c>
       <c r="T50">
-        <v>1.044105062210872</v>
+        <v>1.061553341993807</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.071537050883043</v>
+        <v>2.029260784538491</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08842047046877104</v>
+        <v>0.0937499705529056</v>
       </c>
       <c r="C51">
-        <v>44.30152403545563</v>
+        <v>34.07254150136808</v>
       </c>
       <c r="D51">
-        <v>84.34752403545563</v>
+        <v>74.97254150136808</v>
       </c>
       <c r="E51">
-        <v>-5.153999999999996</v>
+        <v>-4.299999999999997</v>
       </c>
       <c r="F51">
-        <v>41.846</v>
+        <v>42.7</v>
       </c>
       <c r="G51">
         <v>1.8</v>
@@ -5457,45 +5457,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M51">
-        <v>3.1719268</v>
+        <v>3.843</v>
       </c>
       <c r="N51">
-        <v>3.264739866666666</v>
+        <v>2.593666666666667</v>
       </c>
       <c r="O51">
-        <v>0.8161849666666665</v>
+        <v>0.6484166666666666</v>
       </c>
       <c r="P51">
-        <v>2.4485549</v>
+        <v>1.94525</v>
       </c>
       <c r="Q51">
-        <v>5.078554899999999</v>
+        <v>4.57525</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1187528832721001</v>
+        <v>0.1199999411058112</v>
       </c>
       <c r="T51">
-        <v>1.061553341993807</v>
+        <v>1.07969955296806</v>
       </c>
       <c r="U51">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.029260784538491</v>
+        <v>1.67490675687397</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0937499705529056</v>
+        <v>0.09386097063704014</v>
       </c>
       <c r="C52">
-        <v>34.07254150136808</v>
+        <v>33.04538731192649</v>
       </c>
       <c r="D52">
-        <v>74.97254150136808</v>
+        <v>74.79938731192649</v>
       </c>
       <c r="E52">
-        <v>-4.299999999999997</v>
+        <v>-3.445999999999998</v>
       </c>
       <c r="F52">
-        <v>42.7</v>
+        <v>43.554</v>
       </c>
       <c r="G52">
         <v>1.8</v>
@@ -5539,28 +5539,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M52">
-        <v>3.843</v>
+        <v>3.91986</v>
       </c>
       <c r="N52">
-        <v>2.593666666666667</v>
+        <v>2.516806666666667</v>
       </c>
       <c r="O52">
-        <v>0.6484166666666666</v>
+        <v>0.6292016666666667</v>
       </c>
       <c r="P52">
-        <v>1.94525</v>
+        <v>1.887605</v>
       </c>
       <c r="Q52">
-        <v>4.57525</v>
+        <v>4.517605</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1199999411058112</v>
+        <v>0.1212978992592656</v>
       </c>
       <c r="T52">
-        <v>1.07969955296806</v>
+        <v>1.098586425614732</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.67490675687397</v>
+        <v>1.642065447915657</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09386097063704014</v>
+        <v>0.09397197072117469</v>
       </c>
       <c r="C53">
-        <v>33.04538731192649</v>
+        <v>32.01903110227724</v>
       </c>
       <c r="D53">
-        <v>74.79938731192649</v>
+        <v>74.62703110227724</v>
       </c>
       <c r="E53">
-        <v>-3.445999999999998</v>
+        <v>-2.591999999999999</v>
       </c>
       <c r="F53">
-        <v>43.554</v>
+        <v>44.408</v>
       </c>
       <c r="G53">
         <v>1.8</v>
@@ -5621,28 +5621,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M53">
-        <v>3.91986</v>
+        <v>3.99672</v>
       </c>
       <c r="N53">
-        <v>2.516806666666667</v>
+        <v>2.439946666666667</v>
       </c>
       <c r="O53">
-        <v>0.6292016666666667</v>
+        <v>0.6099866666666667</v>
       </c>
       <c r="P53">
-        <v>1.887605</v>
+        <v>1.82996</v>
       </c>
       <c r="Q53">
-        <v>4.517605</v>
+        <v>4.45996</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1212978992592656</v>
+        <v>0.1226499390024473</v>
       </c>
       <c r="T53">
-        <v>1.098586425614732</v>
+        <v>1.118260251288348</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.642065447915657</v>
+        <v>1.610487266224971</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09397197072117469</v>
+        <v>0.09408297080530925</v>
       </c>
       <c r="C54">
-        <v>32.01903110227724</v>
+        <v>30.99346736887592</v>
       </c>
       <c r="D54">
-        <v>74.62703110227724</v>
+        <v>74.45546736887593</v>
       </c>
       <c r="E54">
-        <v>-2.591999999999999</v>
+        <v>-1.737999999999992</v>
       </c>
       <c r="F54">
-        <v>44.408</v>
+        <v>45.26200000000001</v>
       </c>
       <c r="G54">
         <v>1.8</v>
@@ -5703,28 +5703,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M54">
-        <v>3.99672</v>
+        <v>4.073580000000001</v>
       </c>
       <c r="N54">
-        <v>2.439946666666667</v>
+        <v>2.363086666666666</v>
       </c>
       <c r="O54">
-        <v>0.6099866666666667</v>
+        <v>0.5907716666666665</v>
       </c>
       <c r="P54">
-        <v>1.82996</v>
+        <v>1.772314999999999</v>
       </c>
       <c r="Q54">
-        <v>4.45996</v>
+        <v>4.402315</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1226499390024473</v>
+        <v>0.1240595123517218</v>
       </c>
       <c r="T54">
-        <v>1.118260251288348</v>
+        <v>1.138771261033182</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.610487266224971</v>
+        <v>1.580100714032047</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09408297080530925</v>
+        <v>0.09419397088944381</v>
       </c>
       <c r="C55">
-        <v>30.99346736887592</v>
+        <v>29.9686906586716</v>
       </c>
       <c r="D55">
-        <v>74.45546736887593</v>
+        <v>74.28469065867161</v>
       </c>
       <c r="E55">
-        <v>-1.737999999999992</v>
+        <v>-0.8839999999999932</v>
       </c>
       <c r="F55">
-        <v>45.26200000000001</v>
+        <v>46.11600000000001</v>
       </c>
       <c r="G55">
         <v>1.8</v>
@@ -5785,28 +5785,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M55">
-        <v>4.073580000000001</v>
+        <v>4.150440000000001</v>
       </c>
       <c r="N55">
-        <v>2.363086666666666</v>
+        <v>2.286226666666666</v>
       </c>
       <c r="O55">
-        <v>0.5907716666666665</v>
+        <v>0.5715566666666665</v>
       </c>
       <c r="P55">
-        <v>1.772314999999999</v>
+        <v>1.714669999999999</v>
       </c>
       <c r="Q55">
-        <v>4.402315</v>
+        <v>4.344669999999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1240595123517218</v>
+        <v>0.1255303714987909</v>
       </c>
       <c r="T55">
-        <v>1.138771261033182</v>
+        <v>1.1601740538104</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.580100714032047</v>
+        <v>1.55083958969812</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09419397088944381</v>
+        <v>0.09430497097357837</v>
       </c>
       <c r="C56">
-        <v>29.9686906586716</v>
+        <v>28.94469556852889</v>
       </c>
       <c r="D56">
-        <v>74.28469065867161</v>
+        <v>74.1146955685289</v>
       </c>
       <c r="E56">
-        <v>-0.8839999999999932</v>
+        <v>-0.02999999999999403</v>
       </c>
       <c r="F56">
-        <v>46.11600000000001</v>
+        <v>46.97000000000001</v>
       </c>
       <c r="G56">
         <v>1.8</v>
@@ -5867,28 +5867,28 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M56">
-        <v>4.150440000000001</v>
+        <v>4.227300000000001</v>
       </c>
       <c r="N56">
-        <v>2.286226666666666</v>
+        <v>2.209366666666666</v>
       </c>
       <c r="O56">
-        <v>0.5715566666666665</v>
+        <v>0.5523416666666665</v>
       </c>
       <c r="P56">
-        <v>1.714669999999999</v>
+        <v>1.657025</v>
       </c>
       <c r="Q56">
-        <v>4.344669999999999</v>
+        <v>4.287025</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1255303714987909</v>
+        <v>0.1270666021635075</v>
       </c>
       <c r="T56">
-        <v>1.1601740538104</v>
+        <v>1.182528081822162</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.55083958969812</v>
+        <v>1.522642506249063</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09430497097357837</v>
+        <v>0.1204749636358417</v>
       </c>
       <c r="C57">
-        <v>28.94469556852889</v>
+        <v>2.117049988293978</v>
       </c>
       <c r="D57">
-        <v>74.1146955685289</v>
+        <v>48.14104998829399</v>
       </c>
       <c r="E57">
-        <v>-0.02999999999999403</v>
+        <v>0.8240000000000052</v>
       </c>
       <c r="F57">
-        <v>46.97000000000001</v>
+        <v>47.82400000000001</v>
       </c>
       <c r="G57">
         <v>1.8</v>
@@ -5949,45 +5949,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M57">
-        <v>4.227300000000001</v>
+        <v>7.020563200000002</v>
       </c>
       <c r="N57">
-        <v>2.209366666666666</v>
+        <v>-0.583896533333335</v>
       </c>
       <c r="O57">
-        <v>0.5523416666666665</v>
+        <v>-0.1459741333333338</v>
       </c>
       <c r="P57">
-        <v>1.657025</v>
+        <v>-0.4379224000000013</v>
       </c>
       <c r="Q57">
-        <v>4.287025</v>
+        <v>2.192077599999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1270666021635075</v>
+        <v>0.1297946923878952</v>
       </c>
       <c r="T57">
-        <v>1.182528081822162</v>
+        <v>1.222225118663843</v>
       </c>
       <c r="U57">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.25</v>
+        <v>0.2292076320410685</v>
       </c>
       <c r="W57">
-        <v>0.0675</v>
+        <v>0.1131523196163711</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.522642506249063</v>
+        <v>0.9168305281642739</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1204749636358417</v>
+        <v>0.1214849636358417</v>
       </c>
       <c r="C58">
-        <v>2.117049988293978</v>
+        <v>0.6206177513951801</v>
       </c>
       <c r="D58">
-        <v>48.14104998829399</v>
+        <v>47.49861775139519</v>
       </c>
       <c r="E58">
-        <v>0.8240000000000052</v>
+        <v>1.678000000000011</v>
       </c>
       <c r="F58">
-        <v>47.82400000000001</v>
+        <v>48.67800000000001</v>
       </c>
       <c r="G58">
         <v>1.8</v>
@@ -6031,37 +6031,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M58">
-        <v>7.020563200000002</v>
+        <v>7.145930400000003</v>
       </c>
       <c r="N58">
-        <v>-0.583896533333335</v>
+        <v>-0.7092637333333363</v>
       </c>
       <c r="O58">
-        <v>-0.1459741333333338</v>
+        <v>-0.1773159333333341</v>
       </c>
       <c r="P58">
-        <v>-0.4379224000000013</v>
+        <v>-0.5319478000000022</v>
       </c>
       <c r="Q58">
-        <v>2.192077599999998</v>
+        <v>2.098052199999998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1297946923878952</v>
+        <v>0.1317480573271486</v>
       </c>
       <c r="T58">
-        <v>1.222225118663843</v>
+        <v>1.25064895863277</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2292076320410685</v>
+        <v>0.2251864455140322</v>
       </c>
       <c r="W58">
-        <v>0.1131523196163711</v>
+        <v>0.1137426297985401</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.9168305281642739</v>
+        <v>0.9007457820561287</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1214849636358417</v>
+        <v>0.1224949636358418</v>
       </c>
       <c r="C59">
-        <v>0.6206177513951801</v>
+        <v>-0.8588940378364427</v>
       </c>
       <c r="D59">
-        <v>47.49861775139519</v>
+        <v>46.87310596216357</v>
       </c>
       <c r="E59">
-        <v>1.678000000000011</v>
+        <v>2.532000000000011</v>
       </c>
       <c r="F59">
-        <v>48.67800000000001</v>
+        <v>49.53200000000001</v>
       </c>
       <c r="G59">
         <v>1.8</v>
@@ -6113,37 +6113,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M59">
-        <v>7.145930400000003</v>
+        <v>7.271297600000002</v>
       </c>
       <c r="N59">
-        <v>-0.7092637333333363</v>
+        <v>-0.8346309333333357</v>
       </c>
       <c r="O59">
-        <v>-0.1773159333333341</v>
+        <v>-0.2086577333333339</v>
       </c>
       <c r="P59">
-        <v>-0.5319478000000022</v>
+        <v>-0.6259732000000018</v>
       </c>
       <c r="Q59">
-        <v>2.098052199999998</v>
+        <v>2.004026799999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1317480573271486</v>
+        <v>0.1337944396444617</v>
       </c>
       <c r="T59">
-        <v>1.25064895863277</v>
+        <v>1.280426314790693</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2251864455140322</v>
+        <v>0.2213039205913764</v>
       </c>
       <c r="W59">
-        <v>0.1137426297985401</v>
+        <v>0.1143125844571859</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9007457820561287</v>
+        <v>0.8852156823655057</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1224949636358418</v>
+        <v>0.1235049636358417</v>
       </c>
       <c r="C60">
-        <v>-0.8588940378364285</v>
+        <v>-2.322145169381244</v>
       </c>
       <c r="D60">
-        <v>46.87310596216357</v>
+        <v>46.26385483061876</v>
       </c>
       <c r="E60">
-        <v>2.531999999999996</v>
+        <v>3.386000000000003</v>
       </c>
       <c r="F60">
-        <v>49.532</v>
+        <v>50.386</v>
       </c>
       <c r="G60">
         <v>1.8</v>
@@ -6195,37 +6195,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M60">
-        <v>7.2712976</v>
+        <v>7.396664800000001</v>
       </c>
       <c r="N60">
-        <v>-0.8346309333333339</v>
+        <v>-0.9599981333333343</v>
       </c>
       <c r="O60">
-        <v>-0.2086577333333335</v>
+        <v>-0.2399995333333336</v>
       </c>
       <c r="P60">
-        <v>-0.6259732000000005</v>
+        <v>-0.7199986000000007</v>
       </c>
       <c r="Q60">
-        <v>2.004026799999999</v>
+        <v>1.910001399999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1337944396444617</v>
+        <v>0.1359406454894485</v>
       </c>
       <c r="T60">
-        <v>1.280426314790692</v>
+        <v>1.311656224907539</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2213039205913765</v>
+        <v>0.2175530066830481</v>
       </c>
       <c r="W60">
-        <v>0.1143125844571859</v>
+        <v>0.1148632186189286</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.885215682365506</v>
+        <v>0.8702120267321923</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1235049636358417</v>
+        <v>0.1245149636358417</v>
       </c>
       <c r="C61">
-        <v>-2.322145169381244</v>
+        <v>-3.76976156988033</v>
       </c>
       <c r="D61">
-        <v>46.26385483061876</v>
+        <v>45.67023843011967</v>
       </c>
       <c r="E61">
-        <v>3.386000000000003</v>
+        <v>4.240000000000002</v>
       </c>
       <c r="F61">
-        <v>50.386</v>
+        <v>51.24</v>
       </c>
       <c r="G61">
         <v>1.8</v>
@@ -6277,37 +6277,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M61">
-        <v>7.396664800000001</v>
+        <v>7.522032000000001</v>
       </c>
       <c r="N61">
-        <v>-0.9599981333333343</v>
+        <v>-1.085365333333335</v>
       </c>
       <c r="O61">
-        <v>-0.2399995333333336</v>
+        <v>-0.2713413333333337</v>
       </c>
       <c r="P61">
-        <v>-0.7199986000000007</v>
+        <v>-0.814024000000001</v>
       </c>
       <c r="Q61">
-        <v>1.910001399999999</v>
+        <v>1.815975999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1359406454894485</v>
+        <v>0.1381941616266847</v>
       </c>
       <c r="T61">
-        <v>1.311656224907539</v>
+        <v>1.344447630530227</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2175530066830481</v>
+        <v>0.2139271232383306</v>
       </c>
       <c r="W61">
-        <v>0.1148632186189286</v>
+        <v>0.1153954983086131</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8702120267321923</v>
+        <v>0.8557084929533224</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1245149636358417</v>
+        <v>0.1255249636358418</v>
       </c>
       <c r="C62">
-        <v>-3.76976156988033</v>
+        <v>-5.202337447633191</v>
       </c>
       <c r="D62">
-        <v>45.67023843011967</v>
+        <v>45.09166255236681</v>
       </c>
       <c r="E62">
-        <v>4.240000000000002</v>
+        <v>5.094000000000001</v>
       </c>
       <c r="F62">
-        <v>51.24</v>
+        <v>52.094</v>
       </c>
       <c r="G62">
         <v>1.8</v>
@@ -6359,37 +6359,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M62">
-        <v>7.522032000000001</v>
+        <v>7.647399200000001</v>
       </c>
       <c r="N62">
-        <v>-1.085365333333335</v>
+        <v>-1.210732533333334</v>
       </c>
       <c r="O62">
-        <v>-0.2713413333333337</v>
+        <v>-0.3026831333333335</v>
       </c>
       <c r="P62">
-        <v>-0.814024000000001</v>
+        <v>-0.9080494000000006</v>
       </c>
       <c r="Q62">
-        <v>1.815975999999999</v>
+        <v>1.721950599999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1381941616266847</v>
+        <v>0.1405632426940357</v>
       </c>
       <c r="T62">
-        <v>1.344447630530227</v>
+        <v>1.378920646697669</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2139271232383306</v>
+        <v>0.2104201212180301</v>
       </c>
       <c r="W62">
-        <v>0.1153954983086131</v>
+        <v>0.1159103262051932</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8557084929533224</v>
+        <v>0.8416804848721204</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1255249636358418</v>
+        <v>0.1265349636358418</v>
       </c>
       <c r="C63">
-        <v>-5.202337447633191</v>
+        <v>-6.620437276590962</v>
       </c>
       <c r="D63">
-        <v>45.09166255236681</v>
+        <v>44.52756272340904</v>
       </c>
       <c r="E63">
-        <v>5.094000000000001</v>
+        <v>5.948</v>
       </c>
       <c r="F63">
-        <v>52.094</v>
+        <v>52.948</v>
       </c>
       <c r="G63">
         <v>1.8</v>
@@ -6441,37 +6441,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M63">
-        <v>7.647399200000001</v>
+        <v>7.772766400000001</v>
       </c>
       <c r="N63">
-        <v>-1.210732533333334</v>
+        <v>-1.336099733333334</v>
       </c>
       <c r="O63">
-        <v>-0.3026831333333335</v>
+        <v>-0.3340249333333336</v>
       </c>
       <c r="P63">
-        <v>-0.9080494000000006</v>
+        <v>-1.002074800000001</v>
       </c>
       <c r="Q63">
-        <v>1.721950599999999</v>
+        <v>1.627925199999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1405632426940357</v>
+        <v>0.1430570122386156</v>
       </c>
       <c r="T63">
-        <v>1.378920646697669</v>
+        <v>1.415208032137081</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2104201212180301</v>
+        <v>0.2070262482951586</v>
       </c>
       <c r="W63">
-        <v>0.1159103262051932</v>
+        <v>0.1164085467502707</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8416804848721204</v>
+        <v>0.8281049931806346</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1265349636358418</v>
+        <v>0.1275449636358418</v>
       </c>
       <c r="C64">
-        <v>-6.620437276590962</v>
+        <v>-8.02459763327041</v>
       </c>
       <c r="D64">
-        <v>44.52756272340904</v>
+        <v>43.9774023667296</v>
       </c>
       <c r="E64">
-        <v>5.948</v>
+        <v>6.802000000000007</v>
       </c>
       <c r="F64">
-        <v>52.948</v>
+        <v>53.80200000000001</v>
       </c>
       <c r="G64">
         <v>1.8</v>
@@ -6523,37 +6523,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M64">
-        <v>7.772766400000001</v>
+        <v>7.898133600000001</v>
       </c>
       <c r="N64">
-        <v>-1.336099733333334</v>
+        <v>-1.461466933333335</v>
       </c>
       <c r="O64">
-        <v>-0.3340249333333336</v>
+        <v>-0.3653667333333337</v>
       </c>
       <c r="P64">
-        <v>-1.002074800000001</v>
+        <v>-1.096100200000001</v>
       </c>
       <c r="Q64">
-        <v>1.627925199999999</v>
+        <v>1.533899799999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1430570122386156</v>
+        <v>0.1456855801369565</v>
       </c>
       <c r="T64">
-        <v>1.415208032137081</v>
+        <v>1.453456897870516</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2070262482951586</v>
+        <v>0.2037401173698387</v>
       </c>
       <c r="W64">
-        <v>0.1164085467502707</v>
+        <v>0.1168909507701077</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8281049931806346</v>
+        <v>0.8149604694793546</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1275449636358418</v>
+        <v>0.1285549636358418</v>
       </c>
       <c r="C65">
-        <v>-8.02459763327041</v>
+        <v>-9.415328899153778</v>
       </c>
       <c r="D65">
-        <v>43.9774023667296</v>
+        <v>43.44067110084623</v>
       </c>
       <c r="E65">
-        <v>6.802000000000007</v>
+        <v>7.656000000000006</v>
       </c>
       <c r="F65">
-        <v>53.80200000000001</v>
+        <v>54.65600000000001</v>
       </c>
       <c r="G65">
         <v>1.8</v>
@@ -6605,37 +6605,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M65">
-        <v>7.898133600000001</v>
+        <v>8.023500800000001</v>
       </c>
       <c r="N65">
-        <v>-1.461466933333335</v>
+        <v>-1.586834133333334</v>
       </c>
       <c r="O65">
-        <v>-0.3653667333333337</v>
+        <v>-0.3967085333333336</v>
       </c>
       <c r="P65">
-        <v>-1.096100200000001</v>
+        <v>-1.190125600000001</v>
       </c>
       <c r="Q65">
-        <v>1.533899799999999</v>
+        <v>1.439874399999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1456855801369565</v>
+        <v>0.1484601795852053</v>
       </c>
       <c r="T65">
-        <v>1.453456897870516</v>
+        <v>1.493830700589142</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.2037401173698387</v>
+        <v>0.2005566780359349</v>
       </c>
       <c r="W65">
-        <v>0.1168909507701077</v>
+        <v>0.1173582796643248</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8149604694793546</v>
+        <v>0.8022267121437398</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1285549636358418</v>
+        <v>0.1661285308248717</v>
       </c>
       <c r="C66">
-        <v>-9.415328899153778</v>
+        <v>-23.83403348878897</v>
       </c>
       <c r="D66">
-        <v>43.44067110084623</v>
+        <v>29.87596651121104</v>
       </c>
       <c r="E66">
-        <v>7.656000000000006</v>
+        <v>8.510000000000005</v>
       </c>
       <c r="F66">
-        <v>54.65600000000001</v>
+        <v>55.51000000000001</v>
       </c>
       <c r="G66">
         <v>1.8</v>
@@ -6687,45 +6687,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M66">
-        <v>8.023500800000001</v>
+        <v>11.146408</v>
       </c>
       <c r="N66">
-        <v>-1.586834133333334</v>
+        <v>-4.709741333333334</v>
       </c>
       <c r="O66">
-        <v>-0.3967085333333336</v>
+        <v>-1.177435333333334</v>
       </c>
       <c r="P66">
-        <v>-1.190125600000001</v>
+        <v>-3.532306000000001</v>
       </c>
       <c r="Q66">
-        <v>1.439874399999999</v>
+        <v>-0.9023060000000012</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1484601795852053</v>
+        <v>0.1555749481134396</v>
       </c>
       <c r="T66">
-        <v>1.493830700589142</v>
+        <v>1.59735925175674</v>
       </c>
       <c r="U66">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.2005566780359349</v>
+        <v>0.1443663884066209</v>
       </c>
       <c r="W66">
-        <v>0.1173582796643248</v>
+        <v>0.1718112292079505</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8022267121437398</v>
+        <v>0.5774655536264837</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1661285308248717</v>
+        <v>0.1676785308248717</v>
       </c>
       <c r="C67">
-        <v>-23.83403348878897</v>
+        <v>-25.06798349129529</v>
       </c>
       <c r="D67">
-        <v>29.87596651121104</v>
+        <v>29.49601650870472</v>
       </c>
       <c r="E67">
-        <v>8.510000000000005</v>
+        <v>9.364000000000004</v>
       </c>
       <c r="F67">
-        <v>55.51000000000001</v>
+        <v>56.364</v>
       </c>
       <c r="G67">
         <v>1.8</v>
@@ -6769,37 +6769,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M67">
-        <v>11.146408</v>
+        <v>11.3178912</v>
       </c>
       <c r="N67">
-        <v>-4.709741333333334</v>
+        <v>-4.881224533333335</v>
       </c>
       <c r="O67">
-        <v>-1.177435333333334</v>
+        <v>-1.220306133333334</v>
       </c>
       <c r="P67">
-        <v>-3.532306000000001</v>
+        <v>-3.660918400000002</v>
       </c>
       <c r="Q67">
-        <v>-0.9023060000000012</v>
+        <v>-1.030918400000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1555749481134396</v>
+        <v>0.1588036230579525</v>
       </c>
       <c r="T67">
-        <v>1.59735925175674</v>
+        <v>1.644340406220173</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1443663884066209</v>
+        <v>0.1421790188853085</v>
       </c>
       <c r="W67">
-        <v>0.1718112292079505</v>
+        <v>0.1722504530078301</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5774655536264837</v>
+        <v>0.5687160755412338</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1676785308248717</v>
+        <v>0.1692285308248717</v>
       </c>
       <c r="C68">
-        <v>-25.06798349129529</v>
+        <v>-26.29239076490499</v>
       </c>
       <c r="D68">
-        <v>29.49601650870472</v>
+        <v>29.12560923509502</v>
       </c>
       <c r="E68">
-        <v>9.364000000000004</v>
+        <v>10.21800000000001</v>
       </c>
       <c r="F68">
-        <v>56.364</v>
+        <v>57.21800000000001</v>
       </c>
       <c r="G68">
         <v>1.8</v>
@@ -6851,37 +6851,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M68">
-        <v>11.3178912</v>
+        <v>11.4893744</v>
       </c>
       <c r="N68">
-        <v>-4.881224533333335</v>
+        <v>-5.052707733333336</v>
       </c>
       <c r="O68">
-        <v>-1.220306133333334</v>
+        <v>-1.263176933333334</v>
       </c>
       <c r="P68">
-        <v>-3.660918400000002</v>
+        <v>-3.789530800000002</v>
       </c>
       <c r="Q68">
-        <v>-1.030918400000002</v>
+        <v>-1.159530800000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1588036230579525</v>
+        <v>0.1622279752718298</v>
       </c>
       <c r="T68">
-        <v>1.644340406220173</v>
+        <v>1.69416890337836</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1421790188853085</v>
+        <v>0.1400569439765725</v>
       </c>
       <c r="W68">
-        <v>0.1722504530078301</v>
+        <v>0.1726765656495042</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5687160755412338</v>
+        <v>0.5602277759062899</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1692285308248717</v>
+        <v>0.1707785308248717</v>
       </c>
       <c r="C69">
-        <v>-26.29239076490499</v>
+        <v>-27.50761036011417</v>
       </c>
       <c r="D69">
-        <v>29.12560923509502</v>
+        <v>28.76438963988584</v>
       </c>
       <c r="E69">
-        <v>10.21800000000001</v>
+        <v>11.07200000000001</v>
       </c>
       <c r="F69">
-        <v>57.21800000000001</v>
+        <v>58.07200000000001</v>
       </c>
       <c r="G69">
         <v>1.8</v>
@@ -6933,37 +6933,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M69">
-        <v>11.4893744</v>
+        <v>11.6608576</v>
       </c>
       <c r="N69">
-        <v>-5.052707733333336</v>
+        <v>-5.224190933333335</v>
       </c>
       <c r="O69">
-        <v>-1.263176933333334</v>
+        <v>-1.306047733333334</v>
       </c>
       <c r="P69">
-        <v>-3.789530800000002</v>
+        <v>-3.918143200000001</v>
       </c>
       <c r="Q69">
-        <v>-1.159530800000002</v>
+        <v>-1.288143200000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1622279752718298</v>
+        <v>0.1658663494990745</v>
       </c>
       <c r="T69">
-        <v>1.69416890337836</v>
+        <v>1.747111681608934</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1400569439765725</v>
+        <v>0.1379972830357405</v>
       </c>
       <c r="W69">
-        <v>0.1726765656495042</v>
+        <v>0.1730901455664233</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5602277759062899</v>
+        <v>0.5519891321429622</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1707785308248717</v>
+        <v>0.1723285308248717</v>
       </c>
       <c r="C70">
-        <v>-27.50761036011417</v>
+        <v>-28.7139799296584</v>
       </c>
       <c r="D70">
-        <v>28.76438963988584</v>
+        <v>28.41202007034161</v>
       </c>
       <c r="E70">
-        <v>11.07200000000001</v>
+        <v>11.92600000000001</v>
       </c>
       <c r="F70">
-        <v>58.07200000000001</v>
+        <v>58.92600000000001</v>
       </c>
       <c r="G70">
         <v>1.8</v>
@@ -7015,37 +7015,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M70">
-        <v>11.6608576</v>
+        <v>11.8323408</v>
       </c>
       <c r="N70">
-        <v>-5.224190933333335</v>
+        <v>-5.395674133333336</v>
       </c>
       <c r="O70">
-        <v>-1.306047733333334</v>
+        <v>-1.348918533333334</v>
       </c>
       <c r="P70">
-        <v>-3.918143200000001</v>
+        <v>-4.046755600000002</v>
       </c>
       <c r="Q70">
-        <v>-1.288143200000001</v>
+        <v>-1.416755600000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1658663494990745</v>
+        <v>0.1697394575474318</v>
       </c>
       <c r="T70">
-        <v>1.747111681608934</v>
+        <v>1.803470122951158</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1379972830357405</v>
+        <v>0.1359973224120342</v>
       </c>
       <c r="W70">
-        <v>0.1730901455664233</v>
+        <v>0.1734917376596636</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5519891321429622</v>
+        <v>0.5439892896481366</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1723285308248717</v>
+        <v>0.1738785308248717</v>
       </c>
       <c r="C71">
-        <v>-28.7139799296584</v>
+        <v>-29.91182078124691</v>
       </c>
       <c r="D71">
-        <v>28.41202007034161</v>
+        <v>28.0681792187531</v>
       </c>
       <c r="E71">
-        <v>11.92600000000001</v>
+        <v>12.78000000000001</v>
       </c>
       <c r="F71">
-        <v>58.92600000000001</v>
+        <v>59.78000000000001</v>
       </c>
       <c r="G71">
         <v>1.8</v>
@@ -7097,37 +7097,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M71">
-        <v>11.8323408</v>
+        <v>12.003824</v>
       </c>
       <c r="N71">
-        <v>-5.395674133333336</v>
+        <v>-5.567157333333335</v>
       </c>
       <c r="O71">
-        <v>-1.348918533333334</v>
+        <v>-1.391789333333334</v>
       </c>
       <c r="P71">
-        <v>-4.046755600000002</v>
+        <v>-4.175368000000002</v>
       </c>
       <c r="Q71">
-        <v>-1.416755600000002</v>
+        <v>-1.545368000000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1697394575474318</v>
+        <v>0.1738707727990128</v>
       </c>
       <c r="T71">
-        <v>1.803470122951158</v>
+        <v>1.863585793716197</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1359973224120342</v>
+        <v>0.1340545035204337</v>
       </c>
       <c r="W71">
-        <v>0.1734917376596636</v>
+        <v>0.1738818556930969</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5439892896481366</v>
+        <v>0.5362180140817348</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1738785308248717</v>
+        <v>0.1754285308248717</v>
       </c>
       <c r="C72">
-        <v>-29.91182078124691</v>
+        <v>-31.10143885476996</v>
       </c>
       <c r="D72">
-        <v>28.0681792187531</v>
+        <v>27.73256114523004</v>
       </c>
       <c r="E72">
-        <v>12.78000000000001</v>
+        <v>13.63400000000001</v>
       </c>
       <c r="F72">
-        <v>59.78000000000001</v>
+        <v>60.63400000000001</v>
       </c>
       <c r="G72">
         <v>1.8</v>
@@ -7179,37 +7179,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M72">
-        <v>12.003824</v>
+        <v>12.1753072</v>
       </c>
       <c r="N72">
-        <v>-5.567157333333335</v>
+        <v>-5.738640533333336</v>
       </c>
       <c r="O72">
-        <v>-1.391789333333334</v>
+        <v>-1.434660133333334</v>
       </c>
       <c r="P72">
-        <v>-4.175368000000002</v>
+        <v>-4.303980400000002</v>
       </c>
       <c r="Q72">
-        <v>-1.545368000000002</v>
+        <v>-1.673980400000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1738707727990128</v>
+        <v>0.1782870063438064</v>
       </c>
       <c r="T72">
-        <v>1.863585793716197</v>
+        <v>1.927847372809859</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1340545035204337</v>
+        <v>0.1321664119215543</v>
       </c>
       <c r="W72">
-        <v>0.1738818556930969</v>
+        <v>0.1742609844861519</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5362180140817348</v>
+        <v>0.5286656476862173</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1754285308248717</v>
+        <v>0.1769785308248717</v>
       </c>
       <c r="C73">
-        <v>-31.10143885476996</v>
+        <v>-32.28312563022632</v>
       </c>
       <c r="D73">
-        <v>27.73256114523004</v>
+        <v>27.40487436977368</v>
       </c>
       <c r="E73">
-        <v>13.634</v>
+        <v>14.488</v>
       </c>
       <c r="F73">
-        <v>60.634</v>
+        <v>61.488</v>
       </c>
       <c r="G73">
         <v>1.8</v>
@@ -7261,37 +7261,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M73">
-        <v>12.1753072</v>
+        <v>12.3467904</v>
       </c>
       <c r="N73">
-        <v>-5.738640533333334</v>
+        <v>-5.910123733333333</v>
       </c>
       <c r="O73">
-        <v>-1.434660133333334</v>
+        <v>-1.477530933333333</v>
       </c>
       <c r="P73">
-        <v>-4.3039804</v>
+        <v>-4.4325928</v>
       </c>
       <c r="Q73">
-        <v>-1.6739804</v>
+        <v>-1.8025928</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1782870063438063</v>
+        <v>0.1830186851417994</v>
       </c>
       <c r="T73">
-        <v>1.927847372809858</v>
+        <v>1.996699064695924</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1321664119215543</v>
+        <v>0.1303307673115328</v>
       </c>
       <c r="W73">
-        <v>0.1742609844861519</v>
+        <v>0.1746295819238442</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5286656476862175</v>
+        <v>0.521323069246131</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1769785308248717</v>
+        <v>0.1785285308248717</v>
       </c>
       <c r="C74">
-        <v>-32.28312563022632</v>
+        <v>-33.45715897203433</v>
       </c>
       <c r="D74">
-        <v>27.40487436977368</v>
+        <v>27.08484102796568</v>
       </c>
       <c r="E74">
-        <v>14.488</v>
+        <v>15.34200000000001</v>
       </c>
       <c r="F74">
-        <v>61.488</v>
+        <v>62.34200000000001</v>
       </c>
       <c r="G74">
         <v>1.8</v>
@@ -7343,37 +7343,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M74">
-        <v>12.3467904</v>
+        <v>12.5182736</v>
       </c>
       <c r="N74">
-        <v>-5.910123733333333</v>
+        <v>-6.081606933333336</v>
       </c>
       <c r="O74">
-        <v>-1.477530933333333</v>
+        <v>-1.520401733333334</v>
       </c>
       <c r="P74">
-        <v>-4.4325928</v>
+        <v>-4.561205200000002</v>
       </c>
       <c r="Q74">
-        <v>-1.8025928</v>
+        <v>-1.931205200000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1830186851417994</v>
+        <v>0.1881008586655698</v>
       </c>
       <c r="T74">
-        <v>1.996699064695924</v>
+        <v>2.070650881906885</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1303307673115328</v>
+        <v>0.1285454143346624</v>
       </c>
       <c r="W74">
-        <v>0.1746295819238442</v>
+        <v>0.1749880808015998</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.521323069246131</v>
+        <v>0.5141816573386497</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1785285308248717</v>
+        <v>0.1800785308248717</v>
       </c>
       <c r="C75">
-        <v>-33.45715897203433</v>
+        <v>-34.62380391486663</v>
       </c>
       <c r="D75">
-        <v>27.08484102796568</v>
+        <v>26.77219608513338</v>
       </c>
       <c r="E75">
-        <v>15.34200000000001</v>
+        <v>16.19600000000001</v>
       </c>
       <c r="F75">
-        <v>62.34200000000001</v>
+        <v>63.19600000000001</v>
       </c>
       <c r="G75">
         <v>1.8</v>
@@ -7425,37 +7425,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M75">
-        <v>12.5182736</v>
+        <v>12.6897568</v>
       </c>
       <c r="N75">
-        <v>-6.081606933333336</v>
+        <v>-6.253090133333335</v>
       </c>
       <c r="O75">
-        <v>-1.520401733333334</v>
+        <v>-1.563272533333334</v>
       </c>
       <c r="P75">
-        <v>-4.561205200000002</v>
+        <v>-4.689817600000001</v>
       </c>
       <c r="Q75">
-        <v>-1.931205200000002</v>
+        <v>-2.059817600000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1881008586655698</v>
+        <v>0.1935739686142455</v>
       </c>
       <c r="T75">
-        <v>2.070650881906885</v>
+        <v>2.150291300441765</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1285454143346624</v>
+        <v>0.1268083141409508</v>
       </c>
       <c r="W75">
-        <v>0.1749880808015998</v>
+        <v>0.1753368905204971</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5141816573386497</v>
+        <v>0.5072332565638031</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1800785308248717</v>
+        <v>0.1816285308248717</v>
       </c>
       <c r="C76">
-        <v>-34.62380391486663</v>
+        <v>-35.78331339568006</v>
       </c>
       <c r="D76">
-        <v>26.77219608513338</v>
+        <v>26.46668660431995</v>
       </c>
       <c r="E76">
-        <v>16.19600000000001</v>
+        <v>17.05000000000001</v>
       </c>
       <c r="F76">
-        <v>63.19600000000001</v>
+        <v>64.05000000000001</v>
       </c>
       <c r="G76">
         <v>1.8</v>
@@ -7507,37 +7507,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M76">
-        <v>12.6897568</v>
+        <v>12.86124</v>
       </c>
       <c r="N76">
-        <v>-6.253090133333335</v>
+        <v>-6.424573333333336</v>
       </c>
       <c r="O76">
-        <v>-1.563272533333334</v>
+        <v>-1.606143333333334</v>
       </c>
       <c r="P76">
-        <v>-4.689817600000001</v>
+        <v>-4.818430000000002</v>
       </c>
       <c r="Q76">
-        <v>-2.059817600000001</v>
+        <v>-2.188430000000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1935739686142455</v>
+        <v>0.1994849273588154</v>
       </c>
       <c r="T76">
-        <v>2.150291300441765</v>
+        <v>2.236302952459436</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1268083141409508</v>
+        <v>0.1251175366190714</v>
       </c>
       <c r="W76">
-        <v>0.1753368905204971</v>
+        <v>0.1756763986468905</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5072332565638031</v>
+        <v>0.5004701464762857</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1816285308248717</v>
+        <v>0.2103690978635765</v>
       </c>
       <c r="C77">
-        <v>-35.78331339568006</v>
+        <v>-41.25949089144795</v>
       </c>
       <c r="D77">
-        <v>26.46668660431995</v>
+        <v>21.84450910855206</v>
       </c>
       <c r="E77">
-        <v>17.05000000000001</v>
+        <v>17.90400000000001</v>
       </c>
       <c r="F77">
-        <v>64.05000000000001</v>
+        <v>64.90400000000001</v>
       </c>
       <c r="G77">
         <v>1.8</v>
@@ -7589,45 +7589,45 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M77">
-        <v>12.86124</v>
+        <v>15.3043632</v>
       </c>
       <c r="N77">
-        <v>-6.424573333333336</v>
+        <v>-8.867696533333337</v>
       </c>
       <c r="O77">
-        <v>-1.606143333333334</v>
+        <v>-2.216924133333334</v>
       </c>
       <c r="P77">
-        <v>-4.818430000000002</v>
+        <v>-6.650772400000003</v>
       </c>
       <c r="Q77">
-        <v>-2.188430000000002</v>
+        <v>-4.020772400000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1994849273588154</v>
+        <v>0.2083491619933693</v>
       </c>
       <c r="T77">
-        <v>2.236302952459436</v>
+        <v>2.365288367133604</v>
       </c>
       <c r="U77">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1251175366190714</v>
+        <v>0.1051443072565519</v>
       </c>
       <c r="W77">
-        <v>0.1756763986468905</v>
+        <v>0.2110069723489051</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5004701464762857</v>
+        <v>0.4205772290262076</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2103690978635765</v>
+        <v>0.2122690978635765</v>
       </c>
       <c r="C78">
-        <v>-41.25949089144795</v>
+        <v>-42.36281384591162</v>
       </c>
       <c r="D78">
-        <v>21.84450910855206</v>
+        <v>21.59518615408839</v>
       </c>
       <c r="E78">
-        <v>17.90400000000001</v>
+        <v>18.75800000000001</v>
       </c>
       <c r="F78">
-        <v>64.90400000000001</v>
+        <v>65.75800000000001</v>
       </c>
       <c r="G78">
         <v>1.8</v>
@@ -7671,37 +7671,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M78">
-        <v>15.3043632</v>
+        <v>15.5057364</v>
       </c>
       <c r="N78">
-        <v>-8.867696533333337</v>
+        <v>-9.069069733333336</v>
       </c>
       <c r="O78">
-        <v>-2.216924133333334</v>
+        <v>-2.267267433333334</v>
       </c>
       <c r="P78">
-        <v>-6.650772400000003</v>
+        <v>-6.801802300000002</v>
       </c>
       <c r="Q78">
-        <v>-4.020772400000003</v>
+        <v>-4.171802300000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2083491619933693</v>
+        <v>0.2154165168626462</v>
       </c>
       <c r="T78">
-        <v>2.365288367133604</v>
+        <v>2.468126991791586</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1051443072565519</v>
+        <v>0.1037787967727006</v>
       </c>
       <c r="W78">
-        <v>0.2110069723489051</v>
+        <v>0.2113289597209972</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4205772290262076</v>
+        <v>0.4151151870908024</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2122690978635765</v>
+        <v>0.2141690978635765</v>
       </c>
       <c r="C79">
-        <v>-42.36281384591162</v>
+        <v>-43.46050971536394</v>
       </c>
       <c r="D79">
-        <v>21.59518615408839</v>
+        <v>21.35149028463606</v>
       </c>
       <c r="E79">
-        <v>18.75800000000001</v>
+        <v>19.61200000000001</v>
       </c>
       <c r="F79">
-        <v>65.75800000000001</v>
+        <v>66.61200000000001</v>
       </c>
       <c r="G79">
         <v>1.8</v>
@@ -7753,37 +7753,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M79">
-        <v>15.5057364</v>
+        <v>15.7071096</v>
       </c>
       <c r="N79">
-        <v>-9.069069733333336</v>
+        <v>-9.270442933333335</v>
       </c>
       <c r="O79">
-        <v>-2.267267433333334</v>
+        <v>-2.317610733333334</v>
       </c>
       <c r="P79">
-        <v>-6.801802300000002</v>
+        <v>-6.952832200000001</v>
       </c>
       <c r="Q79">
-        <v>-4.171802300000002</v>
+        <v>-4.322832200000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2154165168626462</v>
+        <v>0.2231263585382211</v>
       </c>
       <c r="T79">
-        <v>2.468126991791586</v>
+        <v>2.580314582327567</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1037787967727006</v>
+        <v>0.1024482993781788</v>
       </c>
       <c r="W79">
-        <v>0.2113289597209972</v>
+        <v>0.2116426910066254</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4151151870908024</v>
+        <v>0.4097931975127153</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2141690978635765</v>
+        <v>0.2160690978635765</v>
       </c>
       <c r="C80">
-        <v>-43.46050971536394</v>
+        <v>-44.55276687447165</v>
       </c>
       <c r="D80">
-        <v>21.35149028463606</v>
+        <v>21.11323312552836</v>
       </c>
       <c r="E80">
-        <v>19.61200000000001</v>
+        <v>20.46600000000001</v>
       </c>
       <c r="F80">
-        <v>66.61200000000001</v>
+        <v>67.46600000000001</v>
       </c>
       <c r="G80">
         <v>1.8</v>
@@ -7835,37 +7835,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M80">
-        <v>15.7071096</v>
+        <v>15.9084828</v>
       </c>
       <c r="N80">
-        <v>-9.270442933333335</v>
+        <v>-9.471816133333338</v>
       </c>
       <c r="O80">
-        <v>-2.317610733333334</v>
+        <v>-2.367954033333334</v>
       </c>
       <c r="P80">
-        <v>-6.952832200000001</v>
+        <v>-7.103862100000003</v>
       </c>
       <c r="Q80">
-        <v>-4.322832200000001</v>
+        <v>-4.473862100000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2231263585382211</v>
+        <v>0.2315704708495649</v>
       </c>
       <c r="T80">
-        <v>2.580314582327567</v>
+        <v>2.703186705295546</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1024482993781788</v>
+        <v>0.1011514854619993</v>
       </c>
       <c r="W80">
-        <v>0.2116426910066254</v>
+        <v>0.2119484797280606</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4097931975127153</v>
+        <v>0.4046059418479973</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2160690978635765</v>
+        <v>0.2179690978635765</v>
       </c>
       <c r="C81">
-        <v>-44.55276687447165</v>
+        <v>-45.63976538254475</v>
       </c>
       <c r="D81">
-        <v>21.11323312552836</v>
+        <v>20.88023461745525</v>
       </c>
       <c r="E81">
-        <v>20.46600000000001</v>
+        <v>21.32000000000001</v>
       </c>
       <c r="F81">
-        <v>67.46600000000001</v>
+        <v>68.32000000000001</v>
       </c>
       <c r="G81">
         <v>1.8</v>
@@ -7917,37 +7917,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M81">
-        <v>15.9084828</v>
+        <v>16.109856</v>
       </c>
       <c r="N81">
-        <v>-9.471816133333338</v>
+        <v>-9.673189333333337</v>
       </c>
       <c r="O81">
-        <v>-2.367954033333334</v>
+        <v>-2.418297333333334</v>
       </c>
       <c r="P81">
-        <v>-7.103862100000003</v>
+        <v>-7.254892000000003</v>
       </c>
       <c r="Q81">
-        <v>-4.473862100000003</v>
+        <v>-4.624892000000003</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2315704708495649</v>
+        <v>0.2408589943920432</v>
       </c>
       <c r="T81">
-        <v>2.703186705295546</v>
+        <v>2.838346040560325</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1011514854619993</v>
+        <v>0.09988709189372433</v>
       </c>
       <c r="W81">
-        <v>0.2119484797280606</v>
+        <v>0.2122466237314598</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4046059418479973</v>
+        <v>0.3995483675748973</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2179690978635765</v>
+        <v>0.2198690978635765</v>
       </c>
       <c r="C82">
-        <v>-45.63976538254475</v>
+        <v>-46.72167743735564</v>
       </c>
       <c r="D82">
-        <v>20.88023461745525</v>
+        <v>20.65232256264437</v>
       </c>
       <c r="E82">
-        <v>21.32000000000001</v>
+        <v>22.17400000000001</v>
       </c>
       <c r="F82">
-        <v>68.32000000000001</v>
+        <v>69.17400000000001</v>
       </c>
       <c r="G82">
         <v>1.8</v>
@@ -7999,37 +7999,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M82">
-        <v>16.109856</v>
+        <v>16.3112292</v>
       </c>
       <c r="N82">
-        <v>-9.673189333333337</v>
+        <v>-9.874562533333336</v>
       </c>
       <c r="O82">
-        <v>-2.418297333333334</v>
+        <v>-2.468640633333334</v>
       </c>
       <c r="P82">
-        <v>-7.254892000000003</v>
+        <v>-7.405921900000002</v>
       </c>
       <c r="Q82">
-        <v>-4.624892000000003</v>
+        <v>-4.775921900000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2408589943920432</v>
+        <v>0.2511252572547823</v>
       </c>
       <c r="T82">
-        <v>2.838346040560325</v>
+        <v>2.987732674274025</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.09988709189372433</v>
+        <v>0.09865391791972773</v>
       </c>
       <c r="W82">
-        <v>0.2122466237314598</v>
+        <v>0.2125374061545282</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3995483675748973</v>
+        <v>0.394615671678911</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2198690978635765</v>
+        <v>0.2217690978635765</v>
       </c>
       <c r="C83">
-        <v>-46.72167743735564</v>
+        <v>-47.79866779955802</v>
       </c>
       <c r="D83">
-        <v>20.65232256264437</v>
+        <v>20.42933220044199</v>
       </c>
       <c r="E83">
-        <v>22.17400000000001</v>
+        <v>23.02800000000001</v>
       </c>
       <c r="F83">
-        <v>69.17400000000001</v>
+        <v>70.02800000000001</v>
       </c>
       <c r="G83">
         <v>1.8</v>
@@ -8081,37 +8081,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M83">
-        <v>16.3112292</v>
+        <v>16.5126024</v>
       </c>
       <c r="N83">
-        <v>-9.874562533333336</v>
+        <v>-10.07593573333333</v>
       </c>
       <c r="O83">
-        <v>-2.468640633333334</v>
+        <v>-2.518983933333334</v>
       </c>
       <c r="P83">
-        <v>-7.405921900000002</v>
+        <v>-7.556951800000001</v>
       </c>
       <c r="Q83">
-        <v>-4.775921900000002</v>
+        <v>-4.926951800000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2511252572547823</v>
+        <v>0.2625322159911591</v>
       </c>
       <c r="T83">
-        <v>2.987732674274025</v>
+        <v>3.153717822844806</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.09865391791972773</v>
+        <v>0.09745082135973106</v>
       </c>
       <c r="W83">
-        <v>0.2125374061545282</v>
+        <v>0.2128210963233754</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.394615671678911</v>
+        <v>0.3898032854389243</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2217690978635765</v>
+        <v>0.2236690978635765</v>
       </c>
       <c r="C84">
-        <v>-47.79866779955802</v>
+        <v>-48.87089418990385</v>
       </c>
       <c r="D84">
-        <v>20.42933220044199</v>
+        <v>20.21110581009615</v>
       </c>
       <c r="E84">
-        <v>23.02800000000001</v>
+        <v>23.88200000000001</v>
       </c>
       <c r="F84">
-        <v>70.02800000000001</v>
+        <v>70.88200000000001</v>
       </c>
       <c r="G84">
         <v>1.8</v>
@@ -8163,37 +8163,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M84">
-        <v>16.5126024</v>
+        <v>16.7139756</v>
       </c>
       <c r="N84">
-        <v>-10.07593573333333</v>
+        <v>-10.27730893333333</v>
       </c>
       <c r="O84">
-        <v>-2.518983933333334</v>
+        <v>-2.569327233333333</v>
       </c>
       <c r="P84">
-        <v>-7.556951800000001</v>
+        <v>-7.7079817</v>
       </c>
       <c r="Q84">
-        <v>-4.926951800000001</v>
+        <v>-5.0779817</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2625322159911591</v>
+        <v>0.275281169872992</v>
       </c>
       <c r="T84">
-        <v>3.153717822844806</v>
+        <v>3.339230635953323</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.09745082135973106</v>
+        <v>0.09627671507828853</v>
       </c>
       <c r="W84">
-        <v>0.2128210963233754</v>
+        <v>0.2130979505845396</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3898032854389243</v>
+        <v>0.3851068603131541</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2236690978635765</v>
+        <v>0.2255690978635765</v>
       </c>
       <c r="C85">
-        <v>-48.87089418990385</v>
+        <v>-49.93850766127103</v>
       </c>
       <c r="D85">
-        <v>20.21110581009615</v>
+        <v>19.99749233872898</v>
       </c>
       <c r="E85">
-        <v>23.88200000000001</v>
+        <v>24.73600000000002</v>
       </c>
       <c r="F85">
-        <v>70.88200000000001</v>
+        <v>71.73600000000002</v>
       </c>
       <c r="G85">
         <v>1.8</v>
@@ -8245,37 +8245,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M85">
-        <v>16.7139756</v>
+        <v>16.9153488</v>
       </c>
       <c r="N85">
-        <v>-10.27730893333333</v>
+        <v>-10.47868213333334</v>
       </c>
       <c r="O85">
-        <v>-2.569327233333333</v>
+        <v>-2.619670533333334</v>
       </c>
       <c r="P85">
-        <v>-7.7079817</v>
+        <v>-7.859011600000002</v>
       </c>
       <c r="Q85">
-        <v>-5.0779817</v>
+        <v>-5.229011600000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.275281169872992</v>
+        <v>0.2896237429900541</v>
       </c>
       <c r="T85">
-        <v>3.339230635953323</v>
+        <v>3.547932550700407</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.09627671507828853</v>
+        <v>0.09513056370830889</v>
       </c>
       <c r="W85">
-        <v>0.2130979505845396</v>
+        <v>0.2133682130775808</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3851068603131541</v>
+        <v>0.3805222548332357</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2255690978635765</v>
+        <v>0.2274690978635765</v>
       </c>
       <c r="C86">
-        <v>-49.93850766127102</v>
+        <v>-51.00165294734558</v>
       </c>
       <c r="D86">
-        <v>19.99749233872898</v>
+        <v>19.78834705265442</v>
       </c>
       <c r="E86">
-        <v>24.736</v>
+        <v>25.59</v>
       </c>
       <c r="F86">
-        <v>71.736</v>
+        <v>72.59</v>
       </c>
       <c r="G86">
         <v>1.8</v>
@@ -8327,37 +8327,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M86">
-        <v>16.9153488</v>
+        <v>17.116722</v>
       </c>
       <c r="N86">
-        <v>-10.47868213333333</v>
+        <v>-10.68005533333334</v>
       </c>
       <c r="O86">
-        <v>-2.619670533333333</v>
+        <v>-2.670013833333334</v>
       </c>
       <c r="P86">
-        <v>-7.8590116</v>
+        <v>-8.010041500000002</v>
       </c>
       <c r="Q86">
-        <v>-5.2290116</v>
+        <v>-5.380041500000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2896237429900539</v>
+        <v>0.3058786591893908</v>
       </c>
       <c r="T86">
-        <v>3.547932550700405</v>
+        <v>3.784461387413765</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.09513056370830891</v>
+        <v>0.0940113806058582</v>
       </c>
       <c r="W86">
-        <v>0.2133682130775808</v>
+        <v>0.2136321164531386</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3805222548332357</v>
+        <v>0.3760455224234328</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2274690978635765</v>
+        <v>0.2293690978635765</v>
       </c>
       <c r="C87">
-        <v>-51.00165294734558</v>
+        <v>-52.06046878965029</v>
       </c>
       <c r="D87">
-        <v>19.78834705265442</v>
+        <v>19.58353121034972</v>
       </c>
       <c r="E87">
-        <v>25.59</v>
+        <v>26.444</v>
       </c>
       <c r="F87">
-        <v>72.59</v>
+        <v>73.444</v>
       </c>
       <c r="G87">
         <v>1.8</v>
@@ -8409,37 +8409,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M87">
-        <v>17.116722</v>
+        <v>17.3180952</v>
       </c>
       <c r="N87">
-        <v>-10.68005533333334</v>
+        <v>-10.88142853333333</v>
       </c>
       <c r="O87">
-        <v>-2.670013833333334</v>
+        <v>-2.720357133333334</v>
       </c>
       <c r="P87">
-        <v>-8.010041500000002</v>
+        <v>-8.161071400000001</v>
       </c>
       <c r="Q87">
-        <v>-5.380041500000002</v>
+        <v>-5.531071400000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3058786591893908</v>
+        <v>0.3244557062743473</v>
       </c>
       <c r="T87">
-        <v>3.784461387413765</v>
+        <v>4.05478005794332</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0940113806058582</v>
+        <v>0.09291822501741799</v>
       </c>
       <c r="W87">
-        <v>0.2136321164531386</v>
+        <v>0.2138898825408929</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3760455224234328</v>
+        <v>0.371672900069672</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2293690978635765</v>
+        <v>0.2312690978635765</v>
       </c>
       <c r="C88">
-        <v>-52.06046878965029</v>
+        <v>-53.11508824447199</v>
       </c>
       <c r="D88">
-        <v>19.58353121034972</v>
+        <v>19.38291175552801</v>
       </c>
       <c r="E88">
-        <v>26.444</v>
+        <v>27.298</v>
       </c>
       <c r="F88">
-        <v>73.444</v>
+        <v>74.298</v>
       </c>
       <c r="G88">
         <v>1.8</v>
@@ -8491,37 +8491,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M88">
-        <v>17.3180952</v>
+        <v>17.5194684</v>
       </c>
       <c r="N88">
-        <v>-10.88142853333333</v>
+        <v>-11.08280173333333</v>
       </c>
       <c r="O88">
-        <v>-2.720357133333334</v>
+        <v>-2.770700433333333</v>
       </c>
       <c r="P88">
-        <v>-8.161071400000001</v>
+        <v>-8.3121013</v>
       </c>
       <c r="Q88">
-        <v>-5.531071400000001</v>
+        <v>-5.6821013</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3244557062743473</v>
+        <v>0.3458907606031433</v>
       </c>
       <c r="T88">
-        <v>4.05478005794332</v>
+        <v>4.366686216246651</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09291822501741799</v>
+        <v>0.09185019944250515</v>
       </c>
       <c r="W88">
-        <v>0.2138898825408929</v>
+        <v>0.2141417229714573</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.371672900069672</v>
+        <v>0.3674007977700207</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2312690978635765</v>
+        <v>0.2331690978635765</v>
       </c>
       <c r="C89">
-        <v>-53.11508824447199</v>
+        <v>-54.16563897111484</v>
       </c>
       <c r="D89">
-        <v>19.38291175552801</v>
+        <v>19.18636102888515</v>
       </c>
       <c r="E89">
-        <v>27.298</v>
+        <v>28.152</v>
       </c>
       <c r="F89">
-        <v>74.298</v>
+        <v>75.152</v>
       </c>
       <c r="G89">
         <v>1.8</v>
@@ -8573,37 +8573,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M89">
-        <v>17.5194684</v>
+        <v>17.7208416</v>
       </c>
       <c r="N89">
-        <v>-11.08280173333333</v>
+        <v>-11.28417493333333</v>
       </c>
       <c r="O89">
-        <v>-2.770700433333333</v>
+        <v>-2.821043733333333</v>
       </c>
       <c r="P89">
-        <v>-8.3121013</v>
+        <v>-8.463131199999999</v>
       </c>
       <c r="Q89">
-        <v>-5.6821013</v>
+        <v>-5.8331312</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3458907606031433</v>
+        <v>0.3708983239867387</v>
       </c>
       <c r="T89">
-        <v>4.366686216246651</v>
+        <v>4.730576734267207</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09185019944250515</v>
+        <v>0.09080644717611305</v>
       </c>
       <c r="W89">
-        <v>0.2141417229714573</v>
+        <v>0.2143878397558726</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3674007977700207</v>
+        <v>0.3632257887044522</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2331690978635765</v>
+        <v>0.2350690978635765</v>
       </c>
       <c r="C90">
-        <v>-54.16563897111484</v>
+        <v>-55.21224350279153</v>
       </c>
       <c r="D90">
-        <v>19.18636102888515</v>
+        <v>18.99375649720847</v>
       </c>
       <c r="E90">
-        <v>28.152</v>
+        <v>29.006</v>
       </c>
       <c r="F90">
-        <v>75.152</v>
+        <v>76.006</v>
       </c>
       <c r="G90">
         <v>1.8</v>
@@ -8655,37 +8655,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M90">
-        <v>17.7208416</v>
+        <v>17.9222148</v>
       </c>
       <c r="N90">
-        <v>-11.28417493333333</v>
+        <v>-11.48554813333334</v>
       </c>
       <c r="O90">
-        <v>-2.821043733333333</v>
+        <v>-2.871387033333334</v>
       </c>
       <c r="P90">
-        <v>-8.463131199999999</v>
+        <v>-8.6141611</v>
       </c>
       <c r="Q90">
-        <v>-5.8331312</v>
+        <v>-5.984161100000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3708983239867387</v>
+        <v>0.4004527170764421</v>
       </c>
       <c r="T90">
-        <v>4.730576734267207</v>
+        <v>5.160629164655135</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09080644717611305</v>
+        <v>0.08978615001683087</v>
       </c>
       <c r="W90">
-        <v>0.2143878397558726</v>
+        <v>0.2146284258260313</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3632257887044522</v>
+        <v>0.3591446000673235</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2350690978635765</v>
+        <v>0.2369690978635765</v>
       </c>
       <c r="C91">
-        <v>-55.21224350279153</v>
+        <v>-56.25501950136035</v>
       </c>
       <c r="D91">
-        <v>18.99375649720847</v>
+        <v>18.80498049863966</v>
       </c>
       <c r="E91">
-        <v>29.006</v>
+        <v>29.86000000000001</v>
       </c>
       <c r="F91">
-        <v>76.006</v>
+        <v>76.86000000000001</v>
       </c>
       <c r="G91">
         <v>1.8</v>
@@ -8737,37 +8737,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M91">
-        <v>17.9222148</v>
+        <v>18.12358800000001</v>
       </c>
       <c r="N91">
-        <v>-11.48554813333334</v>
+        <v>-11.68692133333334</v>
       </c>
       <c r="O91">
-        <v>-2.871387033333334</v>
+        <v>-2.921730333333334</v>
       </c>
       <c r="P91">
-        <v>-8.6141611</v>
+        <v>-8.765191000000003</v>
       </c>
       <c r="Q91">
-        <v>-5.984161100000001</v>
+        <v>-6.135191000000003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4004527170764421</v>
+        <v>0.4359179887840863</v>
       </c>
       <c r="T91">
-        <v>5.160629164655135</v>
+        <v>5.676692081120648</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.08978615001683087</v>
+        <v>0.08878852612775495</v>
       </c>
       <c r="W91">
-        <v>0.2146284258260313</v>
+        <v>0.2148636655390754</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3591446000673235</v>
+        <v>0.3551541045110199</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2369690978635765</v>
+        <v>0.2388690978635765</v>
       </c>
       <c r="C92">
-        <v>-56.25501950136035</v>
+        <v>-57.29407999702114</v>
       </c>
       <c r="D92">
-        <v>18.80498049863966</v>
+        <v>18.61992000297887</v>
       </c>
       <c r="E92">
-        <v>29.86000000000001</v>
+        <v>30.71400000000001</v>
       </c>
       <c r="F92">
-        <v>76.86000000000001</v>
+        <v>77.71400000000001</v>
       </c>
       <c r="G92">
         <v>1.8</v>
@@ -8819,37 +8819,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M92">
-        <v>18.12358800000001</v>
+        <v>18.3249612</v>
       </c>
       <c r="N92">
-        <v>-11.68692133333334</v>
+        <v>-11.88829453333334</v>
       </c>
       <c r="O92">
-        <v>-2.921730333333334</v>
+        <v>-2.972073633333334</v>
       </c>
       <c r="P92">
-        <v>-8.765191000000003</v>
+        <v>-8.916220900000003</v>
       </c>
       <c r="Q92">
-        <v>-6.135191000000003</v>
+        <v>-6.286220900000003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4359179887840863</v>
+        <v>0.4792644319823183</v>
       </c>
       <c r="T92">
-        <v>5.676692081120648</v>
+        <v>6.307435645689611</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.08878852612775495</v>
+        <v>0.08781282803843897</v>
       </c>
       <c r="W92">
-        <v>0.2148636655390754</v>
+        <v>0.2150937351485361</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3551541045110199</v>
+        <v>0.3512513121537559</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2388690978635765</v>
+        <v>0.2407690978635765</v>
       </c>
       <c r="C93">
-        <v>-57.29407999702114</v>
+        <v>-58.32953361399595</v>
       </c>
       <c r="D93">
-        <v>18.61992000297887</v>
+        <v>18.43846638600406</v>
       </c>
       <c r="E93">
-        <v>30.71400000000001</v>
+        <v>31.56800000000001</v>
       </c>
       <c r="F93">
-        <v>77.71400000000001</v>
+        <v>78.56800000000001</v>
       </c>
       <c r="G93">
         <v>1.8</v>
@@ -8901,37 +8901,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M93">
-        <v>18.3249612</v>
+        <v>18.5263344</v>
       </c>
       <c r="N93">
-        <v>-11.88829453333334</v>
+        <v>-12.08966773333334</v>
       </c>
       <c r="O93">
-        <v>-2.972073633333334</v>
+        <v>-3.022416933333334</v>
       </c>
       <c r="P93">
-        <v>-8.916220900000003</v>
+        <v>-9.067250800000002</v>
       </c>
       <c r="Q93">
-        <v>-6.286220900000003</v>
+        <v>-6.437250800000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4792644319823183</v>
+        <v>0.5334474859801082</v>
       </c>
       <c r="T93">
-        <v>6.307435645689611</v>
+        <v>7.095865101400814</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.08781282803843897</v>
+        <v>0.0868583407771516</v>
       </c>
       <c r="W93">
-        <v>0.2150937351485361</v>
+        <v>0.2153188032447477</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3512513121537559</v>
+        <v>0.3474333631086064</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2407690978635765</v>
+        <v>0.2426690978635765</v>
       </c>
       <c r="C94">
-        <v>-58.32953361399595</v>
+        <v>-59.36148478314126</v>
       </c>
       <c r="D94">
-        <v>18.43846638600406</v>
+        <v>18.26051521685875</v>
       </c>
       <c r="E94">
-        <v>31.56800000000001</v>
+        <v>32.42200000000001</v>
       </c>
       <c r="F94">
-        <v>78.56800000000001</v>
+        <v>79.42200000000001</v>
       </c>
       <c r="G94">
         <v>1.8</v>
@@ -8983,37 +8983,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M94">
-        <v>18.5263344</v>
+        <v>18.7277076</v>
       </c>
       <c r="N94">
-        <v>-12.08966773333334</v>
+        <v>-12.29104093333333</v>
       </c>
       <c r="O94">
-        <v>-3.022416933333334</v>
+        <v>-3.072760233333334</v>
       </c>
       <c r="P94">
-        <v>-9.067250800000002</v>
+        <v>-9.218280700000001</v>
       </c>
       <c r="Q94">
-        <v>-6.437250800000002</v>
+        <v>-6.588280700000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5334474859801082</v>
+        <v>0.6031114125486952</v>
       </c>
       <c r="T94">
-        <v>7.095865101400814</v>
+        <v>8.109560115886646</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0868583407771516</v>
+        <v>0.08592438012363385</v>
       </c>
       <c r="W94">
-        <v>0.2153188032447477</v>
+        <v>0.2155390311668472</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3474333631086064</v>
+        <v>0.3436975204945354</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2426690978635765</v>
+        <v>0.2445690978635765</v>
       </c>
       <c r="C95">
-        <v>-59.36148478314126</v>
+        <v>-60.39003394236643</v>
       </c>
       <c r="D95">
-        <v>18.26051521685875</v>
+        <v>18.08596605763358</v>
       </c>
       <c r="E95">
-        <v>32.42200000000001</v>
+        <v>33.27600000000001</v>
       </c>
       <c r="F95">
-        <v>79.42200000000001</v>
+        <v>80.27600000000001</v>
       </c>
       <c r="G95">
         <v>1.8</v>
@@ -9065,37 +9065,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M95">
-        <v>18.7277076</v>
+        <v>18.9290808</v>
       </c>
       <c r="N95">
-        <v>-12.29104093333333</v>
+        <v>-12.49241413333334</v>
       </c>
       <c r="O95">
-        <v>-3.072760233333334</v>
+        <v>-3.123103533333334</v>
       </c>
       <c r="P95">
-        <v>-9.218280700000001</v>
+        <v>-9.369310600000002</v>
       </c>
       <c r="Q95">
-        <v>-6.588280700000001</v>
+        <v>-6.739310600000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6031114125486952</v>
+        <v>0.6959966479734777</v>
       </c>
       <c r="T95">
-        <v>8.109560115886646</v>
+        <v>9.461153468534421</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.08592438012363385</v>
+        <v>0.0850102909733824</v>
       </c>
       <c r="W95">
-        <v>0.2155390311668472</v>
+        <v>0.2157545733884764</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3436975204945354</v>
+        <v>0.3400411638935297</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2445690978635765</v>
+        <v>0.2464690978635765</v>
       </c>
       <c r="C96">
-        <v>-60.39003394236643</v>
+        <v>-61.41527772566616</v>
       </c>
       <c r="D96">
-        <v>18.08596605763358</v>
+        <v>17.91472227433385</v>
       </c>
       <c r="E96">
-        <v>33.27600000000001</v>
+        <v>34.13000000000001</v>
       </c>
       <c r="F96">
-        <v>80.27600000000001</v>
+        <v>81.13000000000001</v>
       </c>
       <c r="G96">
         <v>1.8</v>
@@ -9147,37 +9147,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M96">
-        <v>18.9290808</v>
+        <v>19.130454</v>
       </c>
       <c r="N96">
-        <v>-12.49241413333334</v>
+        <v>-12.69378733333334</v>
       </c>
       <c r="O96">
-        <v>-3.123103533333334</v>
+        <v>-3.173446833333334</v>
       </c>
       <c r="P96">
-        <v>-9.369310600000002</v>
+        <v>-9.520340500000003</v>
       </c>
       <c r="Q96">
-        <v>-6.739310600000002</v>
+        <v>-6.890340500000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6959966479734777</v>
+        <v>0.8260359775681737</v>
       </c>
       <c r="T96">
-        <v>9.461153468534421</v>
+        <v>11.35338416224131</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0850102909733824</v>
+        <v>0.08411544580524154</v>
       </c>
       <c r="W96">
-        <v>0.2157545733884764</v>
+        <v>0.215965577879124</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3400411638935297</v>
+        <v>0.3364617832209662</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2464690978635765</v>
+        <v>0.2483690978635765</v>
       </c>
       <c r="C97">
-        <v>-61.41527772566616</v>
+        <v>-62.43730914151499</v>
       </c>
       <c r="D97">
-        <v>17.91472227433385</v>
+        <v>17.74669085848502</v>
       </c>
       <c r="E97">
-        <v>34.13000000000001</v>
+        <v>34.98400000000001</v>
       </c>
       <c r="F97">
-        <v>81.13000000000001</v>
+        <v>81.98400000000001</v>
       </c>
       <c r="G97">
         <v>1.8</v>
@@ -9229,37 +9229,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M97">
-        <v>19.130454</v>
+        <v>19.3318272</v>
       </c>
       <c r="N97">
-        <v>-12.69378733333334</v>
+        <v>-12.89516053333334</v>
       </c>
       <c r="O97">
-        <v>-3.173446833333334</v>
+        <v>-3.223790133333334</v>
       </c>
       <c r="P97">
-        <v>-9.520340500000003</v>
+        <v>-9.671370400000001</v>
       </c>
       <c r="Q97">
-        <v>-6.890340500000003</v>
+        <v>-7.041370400000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8260359775681737</v>
+        <v>1.021094971960218</v>
       </c>
       <c r="T97">
-        <v>11.35338416224131</v>
+        <v>14.19173020280165</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08411544580524154</v>
+        <v>0.08323924324477028</v>
       </c>
       <c r="W97">
-        <v>0.215965577879124</v>
+        <v>0.2161721864428832</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3364617832209662</v>
+        <v>0.3329569729790812</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2483690978635765</v>
+        <v>0.2502690978635765</v>
       </c>
       <c r="C98">
-        <v>-62.43730914151499</v>
+        <v>-63.45621774131531</v>
       </c>
       <c r="D98">
-        <v>17.74669085848502</v>
+        <v>17.58178225868469</v>
       </c>
       <c r="E98">
-        <v>34.98400000000001</v>
+        <v>35.83800000000001</v>
       </c>
       <c r="F98">
-        <v>81.98400000000001</v>
+        <v>82.83800000000001</v>
       </c>
       <c r="G98">
         <v>1.8</v>
@@ -9311,37 +9311,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M98">
-        <v>19.3318272</v>
+        <v>19.5332004</v>
       </c>
       <c r="N98">
-        <v>-12.89516053333334</v>
+        <v>-13.09653373333333</v>
       </c>
       <c r="O98">
-        <v>-3.223790133333334</v>
+        <v>-3.274133433333334</v>
       </c>
       <c r="P98">
-        <v>-9.671370400000001</v>
+        <v>-9.822400300000002</v>
       </c>
       <c r="Q98">
-        <v>-7.041370400000001</v>
+        <v>-7.192400300000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.021094971960215</v>
+        <v>1.346193295946953</v>
       </c>
       <c r="T98">
-        <v>14.19173020280161</v>
+        <v>18.92230693706881</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08323924324477028</v>
+        <v>0.08238110671647368</v>
       </c>
       <c r="W98">
-        <v>0.2161721864428832</v>
+        <v>0.2163745350362555</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3329569729790812</v>
+        <v>0.3295244268658948</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2502690978635765</v>
+        <v>0.2521690978635765</v>
       </c>
       <c r="C99">
-        <v>-63.45621774131531</v>
+        <v>-64.47208977854051</v>
       </c>
       <c r="D99">
-        <v>17.58178225868469</v>
+        <v>17.4199102214595</v>
       </c>
       <c r="E99">
-        <v>35.83800000000001</v>
+        <v>36.69200000000001</v>
       </c>
       <c r="F99">
-        <v>82.83800000000001</v>
+        <v>83.69200000000001</v>
       </c>
       <c r="G99">
         <v>1.8</v>
@@ -9393,37 +9393,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M99">
-        <v>19.5332004</v>
+        <v>19.7345736</v>
       </c>
       <c r="N99">
-        <v>-13.09653373333333</v>
+        <v>-13.29790693333333</v>
       </c>
       <c r="O99">
-        <v>-3.274133433333334</v>
+        <v>-3.324476733333333</v>
       </c>
       <c r="P99">
-        <v>-9.822400300000002</v>
+        <v>-9.973430199999999</v>
       </c>
       <c r="Q99">
-        <v>-7.192400300000002</v>
+        <v>-7.343430199999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.346193295946953</v>
+        <v>1.99638994392043</v>
       </c>
       <c r="T99">
-        <v>18.92230693706881</v>
+        <v>28.38346040560321</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08238110671647368</v>
+        <v>0.08154048317855049</v>
       </c>
       <c r="W99">
-        <v>0.2163745350362555</v>
+        <v>0.2165727540664978</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3295244268658948</v>
+        <v>0.326161932714202</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2521690978635765</v>
+        <v>0.2540690978635765</v>
       </c>
       <c r="C100">
-        <v>-64.47208977854051</v>
+        <v>-65.48500835916667</v>
       </c>
       <c r="D100">
-        <v>17.4199102214595</v>
+        <v>17.26099164083333</v>
       </c>
       <c r="E100">
-        <v>36.69200000000001</v>
+        <v>37.54600000000001</v>
       </c>
       <c r="F100">
-        <v>83.69200000000001</v>
+        <v>84.54600000000001</v>
       </c>
       <c r="G100">
         <v>1.8</v>
@@ -9475,37 +9475,37 @@
         <v>6.436666666666667</v>
       </c>
       <c r="M100">
-        <v>19.7345736</v>
+        <v>19.9359468</v>
       </c>
       <c r="N100">
-        <v>-13.29790693333333</v>
+        <v>-13.49928013333334</v>
       </c>
       <c r="O100">
-        <v>-3.324476733333333</v>
+        <v>-3.374820033333334</v>
       </c>
       <c r="P100">
-        <v>-9.973430199999999</v>
+        <v>-10.1244601</v>
       </c>
       <c r="Q100">
-        <v>-7.343430199999999</v>
+        <v>-7.494460100000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.99638994392043</v>
+        <v>3.946979887840859</v>
       </c>
       <c r="T100">
-        <v>28.38346040560321</v>
+        <v>56.76692081120643</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08154048317855049</v>
+        <v>0.0807168419343227</v>
       </c>
       <c r="W100">
-        <v>0.2165727540664978</v>
+        <v>0.2167669686718867</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.326161932714202</v>
+        <v>0.3228673677372909</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2540690978635765</v>
-      </c>
-      <c r="C101">
-        <v>-65.48500835916667</v>
-      </c>
-      <c r="D101">
-        <v>17.26099164083333</v>
-      </c>
-      <c r="E101">
-        <v>37.54600000000001</v>
-      </c>
-      <c r="F101">
-        <v>84.54600000000001</v>
-      </c>
-      <c r="G101">
-        <v>1.8</v>
-      </c>
-      <c r="H101">
-        <v>38.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.066666666666666</v>
-      </c>
-      <c r="K101">
-        <v>2.63</v>
-      </c>
-      <c r="L101">
-        <v>6.436666666666667</v>
-      </c>
-      <c r="M101">
-        <v>19.9359468</v>
-      </c>
-      <c r="N101">
-        <v>-13.49928013333334</v>
-      </c>
-      <c r="O101">
-        <v>-3.374820033333334</v>
-      </c>
-      <c r="P101">
-        <v>-10.1244601</v>
-      </c>
-      <c r="Q101">
-        <v>-7.494460100000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.946979887840859</v>
-      </c>
-      <c r="T101">
-        <v>56.76692081120643</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0807168419343227</v>
-      </c>
-      <c r="W101">
-        <v>0.2167669686718867</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3228673677372909</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
